--- a/Library/Private/LCSC_Classified/exports/LCSC_Classified_library_index_by_category.xlsx
+++ b/Library/Private/LCSC_Classified/exports/LCSC_Classified_library_index_by_category.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb58c100e43e94c01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacitors" sheetId="2" r:id="R197cc7d4475e46c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Circuit Protection" sheetId="3" r:id="R2e41c094d6094fed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="4" r:id="Rd9bad9d21b644cb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crystals &amp; Oscillators" sheetId="5" r:id="R035686235e124860"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diodes" sheetId="6" r:id="R5b015517498d4406"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Embedded Processors &amp; Controlle" sheetId="7" r:id="Rfae8b7548dd94e4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="8" r:id="R9386f6e4b5f040fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inductors &amp; Coils" sheetId="9" r:id="R28beb8fe3aae4807"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Controls" sheetId="10" r:id="Rf8a261fc863d42a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="11" r:id="R74acfdab702a498a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Magnetic Sensors" sheetId="12" r:id="Rca1f3f65edc54539"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memory" sheetId="13" r:id="R3c9628a32bfd48b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Motor Driver ICs" sheetId="14" r:id="R2d21c5659f3d4dbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Optoelectronics" sheetId="15" r:id="Rd79af87d7f144624"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power Management" sheetId="16" r:id="Rb4aefeda1a3e4eec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resistors" sheetId="17" r:id="Rda6285a2008f4dd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensors" sheetId="18" r:id="R8f04dbd123744c91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Switches" sheetId="19" r:id="R3813780f03a64010"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transistors" sheetId="20" r:id="R2fa13baa767442d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R43c5421822794c8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacitors" sheetId="2" r:id="Re121234c595147d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Circuit Protection" sheetId="3" r:id="R5990811f648e4662"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connectors" sheetId="4" r:id="Reea0365538814731"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crystals &amp; Oscillators" sheetId="5" r:id="Ra9e7c7a17e49419d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diodes" sheetId="6" r:id="Rd6c8a743815c4479"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Embedded Processors &amp; Controlle" sheetId="7" r:id="R9b7c36669a8a412f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="8" r:id="Re2b87c5350f74013"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inductors &amp; Coils" sheetId="9" r:id="R83f4b94ec12e4f51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Controls" sheetId="10" r:id="R2c638f86637c4436"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="11" r:id="R619216d108384103"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Magnetic Sensors" sheetId="12" r:id="Rf26dd93ea0d94301"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memory" sheetId="13" r:id="R18d89abd6b6d474a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Motor Driver ICs" sheetId="14" r:id="Rf9442797c3c54530"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Optoelectronics" sheetId="15" r:id="R17e75cb62a674a79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power Management" sheetId="16" r:id="R8a5debd7a33a4997"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resistors" sheetId="17" r:id="R5c3ff84d06d540a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensors" sheetId="18" r:id="Rfd3a1297730f4e5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Switches" sheetId="19" r:id="Rd32969a0a5f244bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transistors" sheetId="20" r:id="Rf13c74b41b9e43d7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -600,8 +600,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table_LCSCMagneticSensors" displayName="Table_LCSCMagneticSensors" ref="A4:Z7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:Z7"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table_LCSCMagneticSensors" displayName="Table_LCSCMagneticSensors" ref="A4:Z8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:Z8"/>
   <x:tableColumns count="26">
     <x:tableColumn id="1" name="LCSC"/>
     <x:tableColumn id="2" name="MPN"/>
@@ -775,8 +775,8 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="Table_LCSCResistors" displayName="Table_LCSCResistors" ref="A4:Z31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:Z31"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="Table_LCSCResistors" displayName="Table_LCSCResistors" ref="A4:Z34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:Z34"/>
   <x:tableColumns count="26">
     <x:tableColumn id="1" name="LCSC"/>
     <x:tableColumn id="2" name="MPN"/>
@@ -880,8 +880,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table_LCSCCapacitors" displayName="Table_LCSCCapacitors" ref="A4:Z31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:Z31"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table_LCSCCapacitors" displayName="Table_LCSCCapacitors" ref="A4:Z35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:Z35"/>
   <x:tableColumns count="26">
     <x:tableColumn id="1" name="LCSC"/>
     <x:tableColumn id="2" name="MPN"/>
@@ -950,8 +950,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table_LCSCCircuitProtection" displayName="Table_LCSCCircuitProtection" ref="A4:Z5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:Z5"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table_LCSCCircuitProtection" displayName="Table_LCSCCircuitProtection" ref="A4:Z6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:Z6"/>
   <x:tableColumns count="26">
     <x:tableColumn id="1" name="LCSC"/>
     <x:tableColumn id="2" name="MPN"/>
@@ -985,8 +985,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table_LCSCConnectors" displayName="Table_LCSCConnectors" ref="A4:Z11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:Z11"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table_LCSCConnectors" displayName="Table_LCSCConnectors" ref="A4:Z12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:Z12"/>
   <x:tableColumns count="26">
     <x:tableColumn id="1" name="LCSC"/>
     <x:tableColumn id="2" name="MPN"/>
@@ -1443,19 +1443,19 @@
         <x:v>Capacitors</x:v>
       </x:c>
       <x:c r="C5" s="5" t="n">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D5" s="5" t="n">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F5" s="5" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H5" s="5" t="n">
         <x:v>0</x:v>
@@ -1469,19 +1469,19 @@
         <x:v>Circuit Protection</x:v>
       </x:c>
       <x:c r="C6" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D6" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E6" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F6" s="5" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G6" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="5" t="n">
         <x:v>0</x:v>
@@ -1495,19 +1495,19 @@
         <x:v>Connectors</x:v>
       </x:c>
       <x:c r="C7" s="5" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="5" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E7" s="5" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F7" s="5" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G7" s="5" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H7" s="5" t="n">
         <x:v>0</x:v>
@@ -1703,19 +1703,19 @@
         <x:v>Magnetic Sensors</x:v>
       </x:c>
       <x:c r="C15" s="5" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D15" s="5" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E15" s="5" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F15" s="5" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G15" s="5" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H15" s="5" t="n">
         <x:v>0</x:v>
@@ -1833,19 +1833,19 @@
         <x:v>Resistors</x:v>
       </x:c>
       <x:c r="C20" s="5" t="n">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D20" s="5" t="n">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E20" s="5" t="n">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F20" s="5" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G20" s="5" t="n">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H20" s="5" t="n">
         <x:v>0</x:v>
@@ -1932,7 +1932,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23cf6c0748914882"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf60853c09e734b35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2144,7 +2144,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff28e338eff54e74"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bf3c0b5e6e2465a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2500,7 +2500,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6746d777c1f4ff8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54fa86a5c9a6436a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2544,7 +2544,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="str">
-        <x:v>类别：Magnetic Sensors；记录数：3；来源：library_index.csv</x:v>
+        <x:v>类别：Magnetic Sensors；记录数：4；来源：library_index.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2629,43 +2629,39 @@
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="7" t="str">
-        <x:v>C49257133</x:v>
+        <x:v>C2913974</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>MT6701QT-ACD</x:v>
+        <x:v>MT6701QT-STD</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>NOVOSENSE</x:v>
+        <x:v>NOVOSENSE(纳芯微)</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>QFN-16(3x3) Angle, Linear Position Measuring</x:v>
+        <x:v>MT6701 QFN-16 magnetic angle sensor, standard variant</x:v>
       </x:c>
       <x:c r="E5" s="7" t="str">
         <x:v>Magnetic Sensors/Angle, Linear Position Measuring</x:v>
       </x:c>
       <x:c r="F5" s="7" t="str">
-        <x:v>MT6701QT-ACD_C49257133</x:v>
+        <x:v>MT6701QT-STD_C2913974</x:v>
       </x:c>
       <x:c r="G5" s="7" t="str">
         <x:v>VQFN-16_L3.0-W3.0-P0.50-TL-EP1.7</x:v>
       </x:c>
       <x:c r="H5" s="7" t="str">
-        <x:v>暂无料号25</x:v>
+        <x:v>MT6701QT-STD</x:v>
       </x:c>
       <x:c r="I5" s="7" t="str">
-        <x:v>QFN-16(3x3)</x:v>
+        <x:v>QFN-16-EP(3x3)</x:v>
       </x:c>
       <x:c r="J5" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/935357a86952b28e12ac9bd3d186d5d1.pdf?productCode=C49257133</x:v>
-      </x:c>
-      <x:c r="K5" s="7" t="str">
-        <x:v>Rev1.5</x:v>
-      </x:c>
-      <x:c r="L5" s="7" t="str">
-        <x:v>2021-03</x:v>
-      </x:c>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20260616/FEB700C1922508565884FF0A90656B50.pdf</x:v>
+      </x:c>
+      <x:c r="K5" s="7" t="str"/>
+      <x:c r="L5" s="7" t="str"/>
       <x:c r="M5" s="7" t="str">
-        <x:v>../datasheets/C49257133/MT6701_Rev1.5_2021.03.pdf</x:v>
+        <x:v>../datasheets/C2913974/MT6701QT-STD.pdf</x:v>
       </x:c>
       <x:c r="N5" s="7" t="str">
         <x:v>${LCSC_LIB_ROOT}/Magnetic Sensors/Magnetic Sensors.3dshapes/VQFN-16_L3.0-W3.0-H1.0-P0.50.wrl</x:v>
@@ -2677,22 +2673,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q5" s="7" t="str">
-        <x:v>QFN-16/3~5V</x:v>
+        <x:v>QFN-16-EP(3x3)</x:v>
       </x:c>
       <x:c r="R5" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C49257133.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C2913974.html</x:v>
       </x:c>
       <x:c r="S5" s="7" t="str">
-        <x:v>Package: QFN-16(3x3); Operating Temperature: -40℃~+125℃; Number of Conjugate Points of UVW: 16; Supply Current: 10mA; Features: Incremental encoder output;Programmable hysteresis;Magnetic field too high/low warning; Voltage - Supply: 3.3V~5V; Out Type: SSI;ABZ;PWM; Number of ABZ Pulses: 1024; Rotate Speed: 55000rpm; Minimum Field: 20mT</x:v>
+        <x:v>Package: QFN-16(3x3); Supply: 3V~5.5V; Interface: SSI/ABZ/PWM</x:v>
       </x:c>
       <x:c r="T5" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y189.xls; Designators: BOM_PASTER_8984112A_Y189.xls: U1</x:v>
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designator U5.</x:v>
       </x:c>
       <x:c r="U5" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V5" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>EBOM_V1.10</x:v>
       </x:c>
       <x:c r="W5" s="7" t="str">
         <x:v>Magnetic Sensors</x:v>
@@ -2709,42 +2705,46 @@
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="7" t="str">
-        <x:v>C7433196</x:v>
+        <x:v>C49257133</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>MA735GGU-Z</x:v>
+        <x:v>MT6701QT-ACD</x:v>
       </x:c>
       <x:c r="C6" s="7" t="str">
-        <x:v>MPS(芯源)</x:v>
+        <x:v>NOVOSENSE</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>MA735 magnetic angle sensor, QFN-14 2x2mm</x:v>
+        <x:v>QFN-16(3x3) Angle, Linear Position Measuring</x:v>
       </x:c>
       <x:c r="E6" s="7" t="str">
         <x:v>Magnetic Sensors/Angle, Linear Position Measuring</x:v>
       </x:c>
       <x:c r="F6" s="7" t="str">
-        <x:v>MA735GGU-Z</x:v>
+        <x:v>MT6701QT-ACD_C49257133</x:v>
       </x:c>
       <x:c r="G6" s="7" t="str">
-        <x:v>UTQFN-14_L2.0-W2.0-P0.40-TL</x:v>
+        <x:v>VQFN-16_L3.0-W3.0-P0.50-TL-EP1.7</x:v>
       </x:c>
       <x:c r="H6" s="7" t="str">
-        <x:v>MA735GGU-Z</x:v>
+        <x:v>暂无料号25</x:v>
       </x:c>
       <x:c r="I6" s="7" t="str">
-        <x:v>UTQFN-14(2x2)</x:v>
+        <x:v>QFN-16(3x3)</x:v>
       </x:c>
       <x:c r="J6" s="7" t="str">
-        <x:v>https://www.lcsc.com/datasheet/C7433196.pdf</x:v>
-      </x:c>
-      <x:c r="K6" s="7" t="str"/>
-      <x:c r="L6" s="7" t="str"/>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/935357a86952b28e12ac9bd3d186d5d1.pdf?productCode=C49257133</x:v>
+      </x:c>
+      <x:c r="K6" s="7" t="str">
+        <x:v>Rev1.5</x:v>
+      </x:c>
+      <x:c r="L6" s="7" t="str">
+        <x:v>2021-03</x:v>
+      </x:c>
       <x:c r="M6" s="7" t="str">
-        <x:v>../datasheets/C7433196/MA735GGU-Z.pdf</x:v>
+        <x:v>../datasheets/C49257133/MT6701_Rev1.5_2021.03.pdf</x:v>
       </x:c>
       <x:c r="N6" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Magnetic Sensors/Magnetic Sensors.3dshapes/UTQFN-14_L2.0-W2.0-P0.40-TL.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Magnetic Sensors/Magnetic Sensors.3dshapes/VQFN-16_L3.0-W3.0-H1.0-P0.50.wrl</x:v>
       </x:c>
       <x:c r="O6" s="7" t="str">
         <x:v>Active</x:v>
@@ -2753,14 +2753,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q6" s="7" t="str">
-        <x:v>磁性角度传感器</x:v>
+        <x:v>QFN-16/3~5V</x:v>
       </x:c>
       <x:c r="R6" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C7433196.html</x:v>
-      </x:c>
-      <x:c r="S6" s="7" t="str"/>
+        <x:v>https://www.lcsc.com/product-detail/C49257133.html</x:v>
+      </x:c>
+      <x:c r="S6" s="7" t="str">
+        <x:v>Package: QFN-16(3x3); Operating Temperature: -40℃~+125℃; Number of Conjugate Points of UVW: 16; Supply Current: 10mA; Features: Incremental encoder output;Programmable hysteresis;Magnetic field too high/low warning; Voltage - Supply: 3.3V~5V; Out Type: SSI;ABZ;PWM; Number of ABZ Pulses: 1024; Rotate Speed: 55000rpm; Minimum Field: 20mT</x:v>
+      </x:c>
       <x:c r="T6" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y185.xls: U5; Inferred from magnetic angle sensor description; confirm exact device later; Identity and metadata recovered from the existing verified KiCad symbol.</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y189.xls; Designators: BOM_PASTER_8984112A_Y189.xls: U1</x:v>
       </x:c>
       <x:c r="U6" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -2783,42 +2785,42 @@
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="7" t="str">
-        <x:v>C9900009343</x:v>
+        <x:v>C7433196</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>iC-PVL</x:v>
+        <x:v>MA735GGU-Z</x:v>
       </x:c>
       <x:c r="C7" s="7" t="str">
-        <x:v>IC-HAUS</x:v>
+        <x:v>MPS(芯源)</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>iC-PVL QFN16 4x4 Linear Hall Sensor</x:v>
+        <x:v>MA735 magnetic angle sensor, QFN-14 2x2mm</x:v>
       </x:c>
       <x:c r="E7" s="7" t="str">
         <x:v>Magnetic Sensors/Angle, Linear Position Measuring</x:v>
       </x:c>
       <x:c r="F7" s="7" t="str">
-        <x:v>IC-PVL</x:v>
+        <x:v>MA735GGU-Z</x:v>
       </x:c>
       <x:c r="G7" s="7" t="str">
-        <x:v>QFN-16_L4.0-W4.0-P0.65-TL-EP2.7</x:v>
+        <x:v>UTQFN-14_L2.0-W2.0-P0.40-TL</x:v>
       </x:c>
       <x:c r="H7" s="7" t="str">
-        <x:v>iC-PVL</x:v>
+        <x:v>MA735GGU-Z</x:v>
       </x:c>
       <x:c r="I7" s="7" t="str">
-        <x:v>QFN16(4x4)</x:v>
+        <x:v>UTQFN-14(2x2)</x:v>
       </x:c>
       <x:c r="J7" s="7" t="str">
-        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20260917/41A48149B31B33F1461152DD9086207D.pdf</x:v>
+        <x:v>https://www.lcsc.com/datasheet/C7433196.pdf</x:v>
       </x:c>
       <x:c r="K7" s="7" t="str"/>
       <x:c r="L7" s="7" t="str"/>
       <x:c r="M7" s="7" t="str">
-        <x:v>../datasheets/C9900009343/iC-PVL.pdf</x:v>
+        <x:v>../datasheets/C7433196/MA735GGU-Z.pdf</x:v>
       </x:c>
       <x:c r="N7" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Magnetic Sensors/Magnetic Sensors.3dshapes/QFN-16_L4.0-W4.0-H1.0-P0.65.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Magnetic Sensors/Magnetic Sensors.3dshapes/UTQFN-14_L2.0-W2.0-P0.40-TL.wrl</x:v>
       </x:c>
       <x:c r="O7" s="7" t="str">
         <x:v>Active</x:v>
@@ -2827,22 +2829,20 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q7" s="7" t="str">
-        <x:v>QFN16(4x4)</x:v>
+        <x:v>磁性角度传感器</x:v>
       </x:c>
       <x:c r="R7" s="7" t="str">
-        <x:v>https://item.szlcsc.com/217651.html</x:v>
-      </x:c>
-      <x:c r="S7" s="7" t="str">
-        <x:v>Package: QFN16-4x4; Function: linear Hall sensor; Current replacement reference: C46526385</x:v>
-      </x:c>
+        <x:v>https://www.lcsc.com/product-detail/C7433196.html</x:v>
+      </x:c>
+      <x:c r="S7" s="7" t="str"/>
       <x:c r="T7" s="7" t="str">
-        <x:v>Designators: Y193-U2; Y43-U3; Z300BL-U3</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y185.xls: U5; Inferred from magnetic angle sensor description; confirm exact device later; Identity and metadata recovered from the existing verified KiCad symbol.</x:v>
       </x:c>
       <x:c r="U7" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V7" s="7" t="str">
-        <x:v>Y193; Y43; Z300BL</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
       <x:c r="W7" s="7" t="str">
         <x:v>Magnetic Sensors</x:v>
@@ -2857,16 +2857,92 @@
         <x:v>CONVERTED</x:v>
       </x:c>
     </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="7" t="str">
+        <x:v>C9900009343</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="str">
+        <x:v>iC-PVL</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="str">
+        <x:v>IC-HAUS</x:v>
+      </x:c>
+      <x:c r="D8" s="7" t="str">
+        <x:v>iC-PVL QFN16 4x4 Linear Hall Sensor</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="str">
+        <x:v>Magnetic Sensors/Angle, Linear Position Measuring</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="str">
+        <x:v>IC-PVL</x:v>
+      </x:c>
+      <x:c r="G8" s="7" t="str">
+        <x:v>QFN-16_L4.0-W4.0-P0.65-TL-EP2.7</x:v>
+      </x:c>
+      <x:c r="H8" s="7" t="str">
+        <x:v>iC-PVL</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="str">
+        <x:v>QFN16(4x4)</x:v>
+      </x:c>
+      <x:c r="J8" s="7" t="str">
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20260917/41A48149B31B33F1461152DD9086207D.pdf</x:v>
+      </x:c>
+      <x:c r="K8" s="7" t="str"/>
+      <x:c r="L8" s="7" t="str"/>
+      <x:c r="M8" s="7" t="str">
+        <x:v>../datasheets/C9900009343/iC-PVL.pdf</x:v>
+      </x:c>
+      <x:c r="N8" s="7" t="str">
+        <x:v>${LCSC_LIB_ROOT}/Magnetic Sensors/Magnetic Sensors.3dshapes/QFN-16_L4.0-W4.0-H1.0-P0.65.wrl</x:v>
+      </x:c>
+      <x:c r="O8" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P8" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q8" s="7" t="str">
+        <x:v>QFN16(4x4)</x:v>
+      </x:c>
+      <x:c r="R8" s="7" t="str">
+        <x:v>https://item.szlcsc.com/217651.html</x:v>
+      </x:c>
+      <x:c r="S8" s="7" t="str">
+        <x:v>Package: QFN16-4x4; Function: linear Hall sensor; Current replacement reference: C46526385</x:v>
+      </x:c>
+      <x:c r="T8" s="7" t="str">
+        <x:v>Designators: Y193-U2; Y43-U3; Z300BL-U3</x:v>
+      </x:c>
+      <x:c r="U8" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V8" s="7" t="str">
+        <x:v>Y193; Y43; Z300BL</x:v>
+      </x:c>
+      <x:c r="W8" s="7" t="str">
+        <x:v>Magnetic Sensors</x:v>
+      </x:c>
+      <x:c r="X8" s="7" t="str">
+        <x:v>Magnetic Sensors.kicad_sym</x:v>
+      </x:c>
+      <x:c r="Y8" s="7" t="str">
+        <x:v>Magnetic Sensors.pretty</x:v>
+      </x:c>
+      <x:c r="Z8" s="7" t="str">
+        <x:v>CONVERTED</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="U5:U7">
+  <x:conditionalFormatting sqref="U5:U8">
     <x:cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="CLASSIFIED_PARTIAL"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="Z5:Z7">
+  <x:conditionalFormatting sqref="Z5:Z8">
     <x:cfRule type="containsText" dxfId="21" priority="2" operator="containsText" text="PENDING_CONVERSION"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0c2f98fc9bf4c7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra29c4b883a9f4d4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3078,7 +3154,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb7cc1394f8c45b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea4331978d64474e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3444,7 +3520,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61afd7bd47eb49d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6466e753c2b43b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3808,7 +3884,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R587e241e53254afc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb96dce411b964c50"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4394,7 +4470,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf8725dbf0b74f43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R350f21f1eaf2451b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4438,7 +4514,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="str">
-        <x:v>类别：Resistors；记录数：27；来源：library_index.csv</x:v>
+        <x:v>类别：Resistors；记录数：30；来源：library_index.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -4751,42 +4827,42 @@
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>C106225</x:v>
+        <x:v>C106224</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>RC0201FR-0710KL</x:v>
+        <x:v>RC0201FR-07100KL</x:v>
       </x:c>
       <x:c r="C8" s="7" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>YAGEO(国巨)</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>50mW 10kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>100k 1% 0201 chip resistor</x:v>
       </x:c>
       <x:c r="E8" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
-        <x:v>RC0201FR-0710KL</x:v>
+        <x:v>RC0201FR-07100KL</x:v>
       </x:c>
       <x:c r="G8" s="7" t="str">
-        <x:v>R0201</x:v>
+        <x:v>R_0201_0603Metric</x:v>
       </x:c>
       <x:c r="H8" s="7" t="str">
-        <x:v>10kΩ</x:v>
+        <x:v>100k</x:v>
       </x:c>
       <x:c r="I8" s="7" t="str">
         <x:v>0201</x:v>
       </x:c>
       <x:c r="J8" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106225</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20250610/89E4D743C004A82A45145C7A2CC3A578.pdf</x:v>
       </x:c>
       <x:c r="K8" s="7" t="str"/>
       <x:c r="L8" s="7" t="str"/>
       <x:c r="M8" s="7" t="str">
-        <x:v>../datasheets/C106225/RC0201FR-0710KL.pdf</x:v>
+        <x:v>../datasheets/C106224/RC0201FR-07100KL.pdf</x:v>
       </x:c>
       <x:c r="N8" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0201_L0.6-W0.3-H0.3.wrl</x:v>
+        <x:v>${KICAD10_3DMODEL_DIR}/Resistor_SMD.3dshapes/R_0201_0603Metric.step</x:v>
       </x:c>
       <x:c r="O8" s="7" t="str">
         <x:v>Active</x:v>
@@ -4795,22 +4871,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str">
-        <x:v>RC0201FR-0710KL</x:v>
+        <x:v>R0201</x:v>
       </x:c>
       <x:c r="R8" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C106225.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C106224.html</x:v>
       </x:c>
       <x:c r="S8" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 10kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 0201; Resistance: 100k; Tolerance: 1%</x:v>
       </x:c>
       <x:c r="T8" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R2,R32,R33,R39,R49,R50,R51; BOM_PASTER_8984112A_Y185.xls: R2,R3,R4,R7,R9,R11</x:v>
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designator R17.</x:v>
       </x:c>
       <x:c r="U8" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V8" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>EBOM_V1.10</x:v>
       </x:c>
       <x:c r="W8" s="7" t="str">
         <x:v>Resistors</x:v>
@@ -4827,60 +4903,60 @@
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>C106226</x:v>
+        <x:v>C106225</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>RC0201FR-0710RL</x:v>
+        <x:v>RC0201FR-0710KL</x:v>
       </x:c>
       <x:c r="C9" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>50mW 10Ω 25V Thick Film Resistor ±1% -100ppm/℃~+350ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>50mW 10kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F9" s="7" t="str">
-        <x:v>RC0201FR-0710RL</x:v>
+        <x:v>RC0201FR-0710KL</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
         <x:v>R0201</x:v>
       </x:c>
       <x:c r="H9" s="7" t="str">
-        <x:v>10Ω</x:v>
+        <x:v>10kΩ</x:v>
       </x:c>
       <x:c r="I9" s="7" t="str">
         <x:v>0201</x:v>
       </x:c>
       <x:c r="J9" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106226</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106225</x:v>
       </x:c>
       <x:c r="K9" s="7" t="str"/>
       <x:c r="L9" s="7" t="str"/>
       <x:c r="M9" s="7" t="str">
-        <x:v>../datasheets/C106226/RC0201FR-0710RL.pdf</x:v>
+        <x:v>../datasheets/C106225/RC0201FR-0710KL.pdf</x:v>
       </x:c>
       <x:c r="N9" s="7" t="str">
         <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0201_L0.6-W0.3-H0.3.wrl</x:v>
       </x:c>
       <x:c r="O9" s="7" t="str">
-        <x:v>OutOfStock</x:v>
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="P9" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q9" s="7" t="str">
-        <x:v>RC0201FR-0710RL</x:v>
+        <x:v>RC0201FR-0710KL</x:v>
       </x:c>
       <x:c r="R9" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C106226.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C106225.html</x:v>
       </x:c>
       <x:c r="S9" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 10Ω; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: -100ppm/℃~+350ppm/℃</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 10kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
       </x:c>
       <x:c r="T9" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R21,R22; BOM_PASTER_8984112A_Y185.xls: R1,R10</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R2,R32,R33,R39,R49,R50,R51; BOM_PASTER_8984112A_Y185.xls: R2,R3,R4,R7,R9,R11</x:v>
       </x:c>
       <x:c r="U9" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -4903,60 +4979,60 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>C106227</x:v>
+        <x:v>C106226</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>RC0201FR-070RL</x:v>
+        <x:v>RC0201FR-0710RL</x:v>
       </x:c>
       <x:c r="C10" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>50mW 0Ω 25V Thick Film Resistor ±1% 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>50mW 10Ω 25V Thick Film Resistor ±1% -100ppm/℃~+350ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F10" s="7" t="str">
-        <x:v>RC0201FR-070RL</x:v>
+        <x:v>RC0201FR-0710RL</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
         <x:v>R0201</x:v>
       </x:c>
       <x:c r="H10" s="7" t="str">
-        <x:v>0Ω</x:v>
+        <x:v>10Ω</x:v>
       </x:c>
       <x:c r="I10" s="7" t="str">
         <x:v>0201</x:v>
       </x:c>
       <x:c r="J10" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106227</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106226</x:v>
       </x:c>
       <x:c r="K10" s="7" t="str"/>
       <x:c r="L10" s="7" t="str"/>
       <x:c r="M10" s="7" t="str">
-        <x:v>../datasheets/C106227/RC0201FR-070RL.pdf</x:v>
+        <x:v>../datasheets/C106226/RC0201FR-0710RL.pdf</x:v>
       </x:c>
       <x:c r="N10" s="7" t="str">
         <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0201_L0.6-W0.3-H0.3.wrl</x:v>
       </x:c>
       <x:c r="O10" s="7" t="str">
-        <x:v>Active</x:v>
+        <x:v>OutOfStock</x:v>
       </x:c>
       <x:c r="P10" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str">
-        <x:v>RC0201FR-070RL</x:v>
+        <x:v>RC0201FR-0710RL</x:v>
       </x:c>
       <x:c r="R10" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C106227.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C106226.html</x:v>
       </x:c>
       <x:c r="S10" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 0Ω; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: -</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 10Ω; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: -100ppm/℃~+350ppm/℃</x:v>
       </x:c>
       <x:c r="T10" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R8; BOM_PASTER_8984112A_Y185.xls: R12</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R21,R22; BOM_PASTER_8984112A_Y185.xls: R1,R10</x:v>
       </x:c>
       <x:c r="U10" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -4979,42 +5055,42 @@
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>C106231</x:v>
+        <x:v>C106227</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>RC0402FR-070RL</x:v>
+        <x:v>RC0201FR-070RL</x:v>
       </x:c>
       <x:c r="C11" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str">
-        <x:v>0Ω 62.5mW 50V Thick Film Resistor ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>50mW 0Ω 25V Thick Film Resistor ±1% 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F11" s="7" t="str">
-        <x:v>RC0402FR-070RL</x:v>
+        <x:v>RC0201FR-070RL</x:v>
       </x:c>
       <x:c r="G11" s="7" t="str">
-        <x:v>R0402</x:v>
+        <x:v>R0201</x:v>
       </x:c>
       <x:c r="H11" s="7" t="str">
         <x:v>0Ω</x:v>
       </x:c>
       <x:c r="I11" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J11" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106231</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106227</x:v>
       </x:c>
       <x:c r="K11" s="7" t="str"/>
       <x:c r="L11" s="7" t="str"/>
       <x:c r="M11" s="7" t="str">
-        <x:v>../datasheets/C106231/RC0402FR-070RL.pdf</x:v>
+        <x:v>../datasheets/C106227/RC0201FR-070RL.pdf</x:v>
       </x:c>
       <x:c r="N11" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0402_L1.0-W0.5-H0.4.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0201_L0.6-W0.3-H0.3.wrl</x:v>
       </x:c>
       <x:c r="O11" s="7" t="str">
         <x:v>Active</x:v>
@@ -5023,22 +5099,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q11" s="7" t="str">
-        <x:v>贴片电阻</x:v>
+        <x:v>RC0201FR-070RL</x:v>
       </x:c>
       <x:c r="R11" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C106231.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C106227.html</x:v>
       </x:c>
       <x:c r="S11" s="7" t="str">
-        <x:v>Package: 0402; Resistance: 0Ω; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: -; Tolerance: ±1%</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 0Ω; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: -</x:v>
       </x:c>
       <x:c r="T11" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R43,R57</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R8; BOM_PASTER_8984112A_Y185.xls: R12</x:v>
       </x:c>
       <x:c r="U11" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V11" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809; legacy_import</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
       <x:c r="W11" s="7" t="str">
         <x:v>Resistors</x:v>
@@ -5055,39 +5131,39 @@
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>C106235</x:v>
+        <x:v>C106231</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>RC0402FR-071KL</x:v>
+        <x:v>RC0402FR-070RL</x:v>
       </x:c>
       <x:c r="C12" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D12" s="7" t="str">
-        <x:v>1kΩ 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>0Ω 62.5mW 50V Thick Film Resistor ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E12" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F12" s="7" t="str">
-        <x:v>RC0402FR-071KL</x:v>
+        <x:v>RC0402FR-070RL</x:v>
       </x:c>
       <x:c r="G12" s="7" t="str">
         <x:v>R0402</x:v>
       </x:c>
       <x:c r="H12" s="7" t="str">
-        <x:v>1kΩ</x:v>
+        <x:v>0Ω</x:v>
       </x:c>
       <x:c r="I12" s="7" t="str">
         <x:v>0402</x:v>
       </x:c>
       <x:c r="J12" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106235</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106231</x:v>
       </x:c>
       <x:c r="K12" s="7" t="str"/>
       <x:c r="L12" s="7" t="str"/>
       <x:c r="M12" s="7" t="str">
-        <x:v>../datasheets/C106235/RC0402FR-071KL.pdf</x:v>
+        <x:v>../datasheets/C106231/RC0402FR-070RL.pdf</x:v>
       </x:c>
       <x:c r="N12" s="7" t="str">
         <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0402_L1.0-W0.5-H0.4.wrl</x:v>
@@ -5099,16 +5175,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str">
-        <x:v>RC0402FR-071KL</x:v>
+        <x:v>贴片电阻</x:v>
       </x:c>
       <x:c r="R12" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C106235.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C106231.html</x:v>
       </x:c>
       <x:c r="S12" s="7" t="str">
-        <x:v>Package: 0402; Resistance: 1kΩ; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0402; Resistance: 0Ω; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: -; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T12" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R5,R6,R7</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R43,R57</x:v>
       </x:c>
       <x:c r="U12" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -5131,39 +5207,39 @@
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>C138031</x:v>
+        <x:v>C106235</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>RC0402FR-0720RL</x:v>
+        <x:v>RC0402FR-071KL</x:v>
       </x:c>
       <x:c r="C13" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D13" s="7" t="str">
-        <x:v>20Ω 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>1kΩ 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E13" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F13" s="7" t="str">
-        <x:v>RC0402FR-0720RL</x:v>
+        <x:v>RC0402FR-071KL</x:v>
       </x:c>
       <x:c r="G13" s="7" t="str">
         <x:v>R0402</x:v>
       </x:c>
       <x:c r="H13" s="7" t="str">
-        <x:v>20Ω</x:v>
+        <x:v>1kΩ</x:v>
       </x:c>
       <x:c r="I13" s="7" t="str">
         <x:v>0402</x:v>
       </x:c>
       <x:c r="J13" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C138031</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C106235</x:v>
       </x:c>
       <x:c r="K13" s="7" t="str"/>
       <x:c r="L13" s="7" t="str"/>
       <x:c r="M13" s="7" t="str">
-        <x:v>../datasheets/C138031/RC0402FR-0720RL.pdf</x:v>
+        <x:v>../datasheets/C106235/RC0402FR-071KL.pdf</x:v>
       </x:c>
       <x:c r="N13" s="7" t="str">
         <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0402_L1.0-W0.5-H0.4.wrl</x:v>
@@ -5175,22 +5251,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q13" s="7" t="str">
-        <x:v>R0402</x:v>
+        <x:v>RC0402FR-071KL</x:v>
       </x:c>
       <x:c r="R13" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C138031.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C106235.html</x:v>
       </x:c>
       <x:c r="S13" s="7" t="str">
-        <x:v>Package: 0402; Resistance: 20Ω; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0402; Resistance: 1kΩ; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T13" s="7" t="str">
-        <x:v>Designators: R8, R9, R10, R19, R20, R21, R22, R23, R24, R26, R35, R36, R37, R47, R48, R49, R83, R86, R87, R88, R89, R90, R94, R95, R98, R100, R101</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R5,R6,R7</x:v>
       </x:c>
       <x:c r="U13" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V13" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809; legacy_import</x:v>
       </x:c>
       <x:c r="W13" s="7" t="str">
         <x:v>Resistors</x:v>
@@ -5207,42 +5283,42 @@
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>C138135</x:v>
+        <x:v>C114761</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>RC0201FR-074K7L</x:v>
+        <x:v>RC0402FR-0715KL</x:v>
       </x:c>
       <x:c r="C14" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D14" s="7" t="str">
-        <x:v>50mW 4.7kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>15kΩ ±1% 62.5mW 0402 Thick Film Resistor</x:v>
       </x:c>
       <x:c r="E14" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F14" s="7" t="str">
-        <x:v>RC0201FR-074K7L</x:v>
+        <x:v>RC0402FR-0715KL</x:v>
       </x:c>
       <x:c r="G14" s="7" t="str">
-        <x:v>R0201</x:v>
+        <x:v>R_0402_1005Metric</x:v>
       </x:c>
       <x:c r="H14" s="7" t="str">
-        <x:v>4.7kΩ</x:v>
+        <x:v>15kΩ</x:v>
       </x:c>
       <x:c r="I14" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J14" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C138135</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20250610/89E4D743C004A82A45145C7A2CC3A578.pdf</x:v>
       </x:c>
       <x:c r="K14" s="7" t="str"/>
       <x:c r="L14" s="7" t="str"/>
       <x:c r="M14" s="7" t="str">
-        <x:v>../datasheets/C138135/RC0201FR-074K7L.pdf</x:v>
+        <x:v>../datasheets/C114761/RC0402FR-0715KL.pdf</x:v>
       </x:c>
       <x:c r="N14" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0201_L0.6-W0.3-H0.3.wrl</x:v>
+        <x:v>${KICAD10_3DMODEL_DIR}/Resistor_SMD.3dshapes/R_0402_1005Metric.step</x:v>
       </x:c>
       <x:c r="O14" s="7" t="str">
         <x:v>Active</x:v>
@@ -5251,22 +5327,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str">
-        <x:v>RC0201FR-074K7L</x:v>
+        <x:v>R_0402_1005Metric</x:v>
       </x:c>
       <x:c r="R14" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C138135.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C114761.html</x:v>
       </x:c>
       <x:c r="S14" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 4.7kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 0402; Power(Watts): 62.5mW; Resistance: 15kΩ; Voltage Rating: 50V; Type: Thick Film Resistor; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T14" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R20,R48; BOM_PASTER_8984112A_Y185.xls: R21</x:v>
+        <x:v>Added 2026-10-04 for LA150C library rebuild; Value uses master electrical value.</x:v>
       </x:c>
       <x:c r="U14" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V14" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>LocalParts</x:v>
       </x:c>
       <x:c r="W14" s="7" t="str">
         <x:v>Resistors</x:v>
@@ -5283,66 +5359,66 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>C138139</x:v>
+        <x:v>C138031</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>RC0201FR-0747KL</x:v>
+        <x:v>RC0402FR-0720RL</x:v>
       </x:c>
       <x:c r="C15" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D15" s="7" t="str">
-        <x:v>50mW 47kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>20Ω 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E15" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F15" s="7" t="str">
-        <x:v>RC0201FR-0747KL</x:v>
+        <x:v>RC0402FR-0720RL</x:v>
       </x:c>
       <x:c r="G15" s="7" t="str">
-        <x:v>R0201</x:v>
+        <x:v>R0402</x:v>
       </x:c>
       <x:c r="H15" s="7" t="str">
-        <x:v>47kΩ</x:v>
+        <x:v>20Ω</x:v>
       </x:c>
       <x:c r="I15" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J15" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C138139</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C138031</x:v>
       </x:c>
       <x:c r="K15" s="7" t="str"/>
       <x:c r="L15" s="7" t="str"/>
       <x:c r="M15" s="7" t="str">
-        <x:v>../datasheets/C138139/RC0201FR-0747KL.pdf</x:v>
+        <x:v>../datasheets/C138031/RC0402FR-0720RL.pdf</x:v>
       </x:c>
       <x:c r="N15" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0201_L0.6-W0.3-H0.3.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0402_L1.0-W0.5-H0.4.wrl</x:v>
       </x:c>
       <x:c r="O15" s="7" t="str">
-        <x:v>OutOfStock</x:v>
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="P15" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q15" s="7" t="str">
-        <x:v>RC0201FR-0747KL</x:v>
+        <x:v>R0402</x:v>
       </x:c>
       <x:c r="R15" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C138139.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C138031.html</x:v>
       </x:c>
       <x:c r="S15" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 47kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 0402; Resistance: 20Ω; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T15" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R15,R18; BOM_PASTER_8984112A_Y185.xls: R8</x:v>
+        <x:v>Designators: R8, R9, R10, R19, R20, R21, R22, R23, R24, R26, R35, R36, R37, R47, R48, R49, R83, R86, R87, R88, R89, R90, R94, R95, R98, R100, R101</x:v>
       </x:c>
       <x:c r="U15" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V15" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
       <x:c r="W15" s="7" t="str">
         <x:v>Resistors</x:v>
@@ -5359,39 +5435,39 @@
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>C138165</x:v>
+        <x:v>C138135</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>RC0201FR-071KL</x:v>
+        <x:v>RC0201FR-074K7L</x:v>
       </x:c>
       <x:c r="C16" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D16" s="7" t="str">
-        <x:v>50mW 1kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>50mW 4.7kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E16" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F16" s="7" t="str">
-        <x:v>RC0201FR-071KL</x:v>
+        <x:v>RC0201FR-074K7L</x:v>
       </x:c>
       <x:c r="G16" s="7" t="str">
         <x:v>R0201</x:v>
       </x:c>
       <x:c r="H16" s="7" t="str">
-        <x:v>1kΩ</x:v>
+        <x:v>4.7kΩ</x:v>
       </x:c>
       <x:c r="I16" s="7" t="str">
         <x:v>0201</x:v>
       </x:c>
       <x:c r="J16" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C138165</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C138135</x:v>
       </x:c>
       <x:c r="K16" s="7" t="str"/>
       <x:c r="L16" s="7" t="str"/>
       <x:c r="M16" s="7" t="str">
-        <x:v>../datasheets/C138165/RC0201FR-071KL.pdf</x:v>
+        <x:v>../datasheets/C138135/RC0201FR-074K7L.pdf</x:v>
       </x:c>
       <x:c r="N16" s="7" t="str">
         <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0201_L0.6-W0.3-H0.3.wrl</x:v>
@@ -5403,16 +5479,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str">
-        <x:v>RC0201FR-071KL</x:v>
+        <x:v>RC0201FR-074K7L</x:v>
       </x:c>
       <x:c r="R16" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C138165.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C138135.html</x:v>
       </x:c>
       <x:c r="S16" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 1kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 4.7kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
       </x:c>
       <x:c r="T16" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls, BOM_PASTER_8984112A_Y189.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R35,R36; BOM_PASTER_8984112A_Y185.xls: R23; BOM_PASTER_8984112A_Y189.xls: R1</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R20,R48; BOM_PASTER_8984112A_Y185.xls: R21</x:v>
       </x:c>
       <x:c r="U16" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -5435,66 +5511,66 @@
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
       <x:c r="A17" s="7" t="str">
-        <x:v>C144651</x:v>
+        <x:v>C138139</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
-        <x:v>AC0603FR-074R7L</x:v>
+        <x:v>RC0201FR-0747KL</x:v>
       </x:c>
       <x:c r="C17" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D17" s="7" t="str">
-        <x:v>4.7Ω 100mW 75V Thick Film Resistor ±1% ±200ppm/℃ 0603 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>50mW 47kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E17" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F17" s="7" t="str">
-        <x:v>AC0603FR-074R7L</x:v>
+        <x:v>RC0201FR-0747KL</x:v>
       </x:c>
       <x:c r="G17" s="7" t="str">
-        <x:v>R0603</x:v>
+        <x:v>R0201</x:v>
       </x:c>
       <x:c r="H17" s="7" t="str">
-        <x:v>4.7Ω</x:v>
+        <x:v>47kΩ</x:v>
       </x:c>
       <x:c r="I17" s="7" t="str">
-        <x:v>0603</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J17" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/3511efb0564cb1711d9237ab09d6e97b.pdf?productCode=C144651</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C138139</x:v>
       </x:c>
       <x:c r="K17" s="7" t="str"/>
       <x:c r="L17" s="7" t="str"/>
       <x:c r="M17" s="7" t="str">
-        <x:v>../datasheets/C144651/AC0603FR-074R7L.pdf</x:v>
+        <x:v>../datasheets/C138139/RC0201FR-0747KL.pdf</x:v>
       </x:c>
       <x:c r="N17" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0603.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0201_L0.6-W0.3-H0.3.wrl</x:v>
       </x:c>
       <x:c r="O17" s="7" t="str">
-        <x:v>Active</x:v>
+        <x:v>OutOfStock</x:v>
       </x:c>
       <x:c r="P17" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q17" s="7" t="str">
-        <x:v>R0603</x:v>
+        <x:v>RC0201FR-0747KL</x:v>
       </x:c>
       <x:c r="R17" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C144651.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C138139.html</x:v>
       </x:c>
       <x:c r="S17" s="7" t="str">
-        <x:v>Package: 0603; Resistance: 4.7Ω; Power(Watts): 100mW; Voltage Rating: 75V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 47kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
       </x:c>
       <x:c r="T17" s="7" t="str">
-        <x:v>Designators: R32, R33, R34, R44, R45, R46</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R15,R18; BOM_PASTER_8984112A_Y185.xls: R8</x:v>
       </x:c>
       <x:c r="U17" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V17" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
       <x:c r="W17" s="7" t="str">
         <x:v>Resistors</x:v>
@@ -5511,42 +5587,42 @@
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18" s="7" t="str">
-        <x:v>C14675</x:v>
+        <x:v>C138165</x:v>
       </x:c>
       <x:c r="B18" s="7" t="str">
-        <x:v>RC0603FR-07100KL</x:v>
+        <x:v>RC0201FR-071KL</x:v>
       </x:c>
       <x:c r="C18" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D18" s="7" t="str">
-        <x:v>100mW 100kΩ 75V Thick Film Resistor ±100ppm/℃ ±1% 0603 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>50mW 1kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E18" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F18" s="7" t="str">
-        <x:v>RC0603FR-07100KL</x:v>
+        <x:v>RC0201FR-071KL</x:v>
       </x:c>
       <x:c r="G18" s="7" t="str">
-        <x:v>R0603</x:v>
+        <x:v>R0201</x:v>
       </x:c>
       <x:c r="H18" s="7" t="str">
-        <x:v>100kΩ</x:v>
+        <x:v>1kΩ</x:v>
       </x:c>
       <x:c r="I18" s="7" t="str">
-        <x:v>0603</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J18" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C14675</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C138165</x:v>
       </x:c>
       <x:c r="K18" s="7" t="str"/>
       <x:c r="L18" s="7" t="str"/>
       <x:c r="M18" s="7" t="str">
-        <x:v>../datasheets/C14675/RC0603FR-07100KL.pdf</x:v>
+        <x:v>../datasheets/C138165/RC0201FR-071KL.pdf</x:v>
       </x:c>
       <x:c r="N18" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0603.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0201_L0.6-W0.3-H0.3.wrl</x:v>
       </x:c>
       <x:c r="O18" s="7" t="str">
         <x:v>Active</x:v>
@@ -5555,22 +5631,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q18" s="7" t="str">
-        <x:v>R0603</x:v>
+        <x:v>RC0201FR-071KL</x:v>
       </x:c>
       <x:c r="R18" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C138165.html</x:v>
       </x:c>
       <x:c r="S18" s="7" t="str">
-        <x:v>Package: 0603; Power(Watts): 100mW; Resistance: 100kΩ; Voltage Rating: 75V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 1kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
       </x:c>
       <x:c r="T18" s="7" t="str">
-        <x:v>Designators: R68</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls, BOM_PASTER_8984112A_Y189.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R35,R36; BOM_PASTER_8984112A_Y185.xls: R23; BOM_PASTER_8984112A_Y189.xls: R1</x:v>
       </x:c>
       <x:c r="U18" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V18" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
       <x:c r="W18" s="7" t="str">
         <x:v>Resistors</x:v>
@@ -5587,42 +5663,42 @@
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
       <x:c r="A19" s="7" t="str">
-        <x:v>C163437</x:v>
+        <x:v>C144651</x:v>
       </x:c>
       <x:c r="B19" s="7" t="str">
-        <x:v>RC0402JR-0762RL</x:v>
+        <x:v>AC0603FR-074R7L</x:v>
       </x:c>
       <x:c r="C19" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D19" s="7" t="str">
-        <x:v>62Ω 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±5% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>4.7Ω 100mW 75V Thick Film Resistor ±1% ±200ppm/℃ 0603 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E19" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F19" s="7" t="str">
-        <x:v>RC0402JR-0762RL</x:v>
+        <x:v>AC0603FR-074R7L</x:v>
       </x:c>
       <x:c r="G19" s="7" t="str">
-        <x:v>R0402</x:v>
+        <x:v>R0603</x:v>
       </x:c>
       <x:c r="H19" s="7" t="str">
-        <x:v>62Ω</x:v>
+        <x:v>4.7Ω</x:v>
       </x:c>
       <x:c r="I19" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>0603</x:v>
       </x:c>
       <x:c r="J19" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C163437</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/3511efb0564cb1711d9237ab09d6e97b.pdf?productCode=C144651</x:v>
       </x:c>
       <x:c r="K19" s="7" t="str"/>
       <x:c r="L19" s="7" t="str"/>
       <x:c r="M19" s="7" t="str">
-        <x:v>../datasheets/C163437/RC0402JR-0762RL.pdf</x:v>
+        <x:v>../datasheets/C144651/AC0603FR-074R7L.pdf</x:v>
       </x:c>
       <x:c r="N19" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0402_L1.0-W0.5-H0.4.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0603.wrl</x:v>
       </x:c>
       <x:c r="O19" s="7" t="str">
         <x:v>Active</x:v>
@@ -5631,16 +5707,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q19" s="7" t="str">
-        <x:v>R0402</x:v>
+        <x:v>R0603</x:v>
       </x:c>
       <x:c r="R19" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C163437.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C144651.html</x:v>
       </x:c>
       <x:c r="S19" s="7" t="str">
-        <x:v>Package: 0402; Resistance: 62Ω; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±5%</x:v>
+        <x:v>Package: 0603; Resistance: 4.7Ω; Power(Watts): 100mW; Voltage Rating: 75V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
       </x:c>
       <x:c r="T19" s="7" t="str">
-        <x:v>Designators: R13, R14, R96, R97</x:v>
+        <x:v>Designators: R32, R33, R34, R44, R45, R46</x:v>
       </x:c>
       <x:c r="U19" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -5663,42 +5739,42 @@
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="7" t="str">
-        <x:v>C25744</x:v>
+        <x:v>C14675</x:v>
       </x:c>
       <x:c r="B20" s="7" t="str">
-        <x:v>0402WGF1002TCE</x:v>
+        <x:v>RC0603FR-07100KL</x:v>
       </x:c>
       <x:c r="C20" s="7" t="str">
-        <x:v>UNI-ROYAL</x:v>
+        <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D20" s="7" t="str">
-        <x:v>10kΩ ±1% 62.5mW Thick Film Resistor</x:v>
+        <x:v>100mW 100kΩ 75V Thick Film Resistor ±100ppm/℃ ±1% 0603 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E20" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F20" s="7" t="str">
-        <x:v>0402WGF1002TCE</x:v>
+        <x:v>RC0603FR-07100KL</x:v>
       </x:c>
       <x:c r="G20" s="7" t="str">
-        <x:v>R0402</x:v>
+        <x:v>R0603</x:v>
       </x:c>
       <x:c r="H20" s="7" t="str">
-        <x:v>10kΩ</x:v>
+        <x:v>100kΩ</x:v>
       </x:c>
       <x:c r="I20" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>0603</x:v>
       </x:c>
       <x:c r="J20" s="7" t="str">
-        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20200306/C422600_1E6D84923E4A46A82E41ADD87F860B5C.pdf</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C14675</x:v>
       </x:c>
       <x:c r="K20" s="7" t="str"/>
       <x:c r="L20" s="7" t="str"/>
       <x:c r="M20" s="7" t="str">
-        <x:v>../datasheets/C25744/0402WGF1002TCE.pdf</x:v>
+        <x:v>../datasheets/C14675/RC0603FR-07100KL.pdf</x:v>
       </x:c>
       <x:c r="N20" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0402_L1.0-W0.5-H0.4.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0603.wrl</x:v>
       </x:c>
       <x:c r="O20" s="7" t="str">
         <x:v>Active</x:v>
@@ -5707,22 +5783,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q20" s="7" t="str">
-        <x:v>0402-10K-1%</x:v>
+        <x:v>R0603</x:v>
       </x:c>
       <x:c r="R20" s="7" t="str">
-        <x:v>https://item.szlcsc.com/26487.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C14675.html</x:v>
       </x:c>
       <x:c r="S20" s="7" t="str">
-        <x:v>Package: 0402; Resistance: 10kΩ; Tolerance: ±1%; Power: 62.5mW</x:v>
+        <x:v>Package: 0603; Power(Watts): 100mW; Resistance: 100kΩ; Voltage Rating: 75V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T20" s="7" t="str">
-        <x:v>Designators: Y43-R3,R4,R5,R6,R7</x:v>
+        <x:v>Designators: R68</x:v>
       </x:c>
       <x:c r="U20" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V20" s="7" t="str">
-        <x:v>Y43</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
       <x:c r="W20" s="7" t="str">
         <x:v>Resistors</x:v>
@@ -5739,39 +5815,39 @@
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
       <x:c r="A21" s="7" t="str">
-        <x:v>C273722</x:v>
+        <x:v>C163437</x:v>
       </x:c>
       <x:c r="B21" s="7" t="str">
-        <x:v>RC0402FR-07768KL</x:v>
+        <x:v>RC0402JR-0762RL</x:v>
       </x:c>
       <x:c r="C21" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D21" s="7" t="str">
-        <x:v>768kΩ 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>62Ω 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±5% 0402 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E21" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F21" s="7" t="str">
-        <x:v>RC0402FR-07768KL</x:v>
+        <x:v>RC0402JR-0762RL</x:v>
       </x:c>
       <x:c r="G21" s="7" t="str">
         <x:v>R0402</x:v>
       </x:c>
       <x:c r="H21" s="7" t="str">
-        <x:v>768kΩ</x:v>
+        <x:v>62Ω</x:v>
       </x:c>
       <x:c r="I21" s="7" t="str">
         <x:v>0402</x:v>
       </x:c>
       <x:c r="J21" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C273722</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C163437</x:v>
       </x:c>
       <x:c r="K21" s="7" t="str"/>
       <x:c r="L21" s="7" t="str"/>
       <x:c r="M21" s="7" t="str">
-        <x:v>../datasheets/C273722/RC0402FR-07768KL.pdf</x:v>
+        <x:v>../datasheets/C163437/RC0402JR-0762RL.pdf</x:v>
       </x:c>
       <x:c r="N21" s="7" t="str">
         <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0402_L1.0-W0.5-H0.4.wrl</x:v>
@@ -5786,13 +5862,13 @@
         <x:v>R0402</x:v>
       </x:c>
       <x:c r="R21" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C273722.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C163437.html</x:v>
       </x:c>
       <x:c r="S21" s="7" t="str">
-        <x:v>Package: 0402; Resistance: 768kΩ; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0402; Resistance: 62Ω; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±5%</x:v>
       </x:c>
       <x:c r="T21" s="7" t="str">
-        <x:v>Designators: R2</x:v>
+        <x:v>Designators: R13, R14, R96, R97</x:v>
       </x:c>
       <x:c r="U21" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -5815,42 +5891,42 @@
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
       <x:c r="A22" s="7" t="str">
-        <x:v>C274877</x:v>
+        <x:v>C25744</x:v>
       </x:c>
       <x:c r="B22" s="7" t="str">
-        <x:v>RC0201FR-076K8L</x:v>
+        <x:v>0402WGF1002TCE</x:v>
       </x:c>
       <x:c r="C22" s="7" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>UNI-ROYAL</x:v>
       </x:c>
       <x:c r="D22" s="7" t="str">
-        <x:v>50mW 6.8kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>10kΩ ±1% 62.5mW Thick Film Resistor</x:v>
       </x:c>
       <x:c r="E22" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F22" s="7" t="str">
-        <x:v>RC0201FR-076K8L</x:v>
+        <x:v>0402WGF1002TCE</x:v>
       </x:c>
       <x:c r="G22" s="7" t="str">
-        <x:v>R0201</x:v>
+        <x:v>R0402</x:v>
       </x:c>
       <x:c r="H22" s="7" t="str">
-        <x:v>6.8kΩ</x:v>
+        <x:v>10kΩ</x:v>
       </x:c>
       <x:c r="I22" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J22" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C274877</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20200306/C422600_1E6D84923E4A46A82E41ADD87F860B5C.pdf</x:v>
       </x:c>
       <x:c r="K22" s="7" t="str"/>
       <x:c r="L22" s="7" t="str"/>
       <x:c r="M22" s="7" t="str">
-        <x:v>../datasheets/C274877/RC0201FR-076K8L.pdf</x:v>
+        <x:v>../datasheets/C25744/0402WGF1002TCE.pdf</x:v>
       </x:c>
       <x:c r="N22" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0201_L0.6-W0.3-H0.3.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0402_L1.0-W0.5-H0.4.wrl</x:v>
       </x:c>
       <x:c r="O22" s="7" t="str">
         <x:v>Active</x:v>
@@ -5859,22 +5935,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q22" s="7" t="str">
-        <x:v>RC0201FR-076K8L</x:v>
+        <x:v>0402-10K-1%</x:v>
       </x:c>
       <x:c r="R22" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C274877.html</x:v>
+        <x:v>https://item.szlcsc.com/26487.html</x:v>
       </x:c>
       <x:c r="S22" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 6.8kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 0402; Resistance: 10kΩ; Tolerance: ±1%; Power: 62.5mW</x:v>
       </x:c>
       <x:c r="T22" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R13,R47; BOM_PASTER_8984112A_Y185.xls: R17</x:v>
+        <x:v>Designators: Y43-R3,R4,R5,R6,R7</x:v>
       </x:c>
       <x:c r="U22" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V22" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>Y43</x:v>
       </x:c>
       <x:c r="W22" s="7" t="str">
         <x:v>Resistors</x:v>
@@ -5891,66 +5967,66 @@
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
       <x:c r="A23" s="7" t="str">
-        <x:v>C474825</x:v>
+        <x:v>C273722</x:v>
       </x:c>
       <x:c r="B23" s="7" t="str">
-        <x:v>RC0201FR-0776K8L</x:v>
+        <x:v>RC0402FR-07768KL</x:v>
       </x:c>
       <x:c r="C23" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D23" s="7" t="str">
-        <x:v>50mW 76.8kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>768kΩ 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E23" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F23" s="7" t="str">
-        <x:v>RC0201FR-0776K8L</x:v>
+        <x:v>RC0402FR-07768KL</x:v>
       </x:c>
       <x:c r="G23" s="7" t="str">
-        <x:v>R_0201_0603Metric</x:v>
+        <x:v>R0402</x:v>
       </x:c>
       <x:c r="H23" s="7" t="str">
-        <x:v>76.8kΩ</x:v>
+        <x:v>768kΩ</x:v>
       </x:c>
       <x:c r="I23" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J23" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C474825</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C273722</x:v>
       </x:c>
       <x:c r="K23" s="7" t="str"/>
       <x:c r="L23" s="7" t="str"/>
       <x:c r="M23" s="7" t="str">
-        <x:v>../datasheets/C474825/RC0201FR-0776K8L.pdf</x:v>
+        <x:v>../datasheets/C273722/RC0402FR-07768KL.pdf</x:v>
       </x:c>
       <x:c r="N23" s="7" t="str">
-        <x:v>${KICAD10_3DMODEL_DIR}/Resistor_SMD.3dshapes/R_0201_0603Metric.step</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0402_L1.0-W0.5-H0.4.wrl</x:v>
       </x:c>
       <x:c r="O23" s="7" t="str">
-        <x:v>OutOfStock</x:v>
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="P23" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q23" s="7" t="str">
-        <x:v>RC0201FR-0776K8L</x:v>
+        <x:v>R0402</x:v>
       </x:c>
       <x:c r="R23" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C474825.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C273722.html</x:v>
       </x:c>
       <x:c r="S23" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 76.8kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 0402; Resistance: 768kΩ; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T23" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R17</x:v>
+        <x:v>Designators: R2</x:v>
       </x:c>
       <x:c r="U23" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V23" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
       <x:c r="W23" s="7" t="str">
         <x:v>Resistors</x:v>
@@ -5967,42 +6043,42 @@
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
       <x:c r="A24" s="7" t="str">
-        <x:v>C60490</x:v>
+        <x:v>C274877</x:v>
       </x:c>
       <x:c r="B24" s="7" t="str">
-        <x:v>RC0402FR-0710KL</x:v>
+        <x:v>RC0201FR-076K8L</x:v>
       </x:c>
       <x:c r="C24" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D24" s="7" t="str">
-        <x:v>62.5mW 10kΩ 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>50mW 6.8kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E24" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F24" s="7" t="str">
-        <x:v>RC0402FR-0710KL</x:v>
+        <x:v>RC0201FR-076K8L</x:v>
       </x:c>
       <x:c r="G24" s="7" t="str">
-        <x:v>R0402</x:v>
+        <x:v>R0201</x:v>
       </x:c>
       <x:c r="H24" s="7" t="str">
-        <x:v>10kΩ</x:v>
+        <x:v>6.8kΩ</x:v>
       </x:c>
       <x:c r="I24" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J24" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C60490</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C274877</x:v>
       </x:c>
       <x:c r="K24" s="7" t="str"/>
       <x:c r="L24" s="7" t="str"/>
       <x:c r="M24" s="7" t="str">
-        <x:v>../datasheets/C60490/RC0402FR-0710KL.pdf</x:v>
+        <x:v>../datasheets/C274877/RC0201FR-076K8L.pdf</x:v>
       </x:c>
       <x:c r="N24" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0402_L1.0-W0.5-H0.4.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0201_L0.6-W0.3-H0.3.wrl</x:v>
       </x:c>
       <x:c r="O24" s="7" t="str">
         <x:v>Active</x:v>
@@ -6011,22 +6087,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q24" s="7" t="str">
-        <x:v>R0402</x:v>
+        <x:v>RC0201FR-076K8L</x:v>
       </x:c>
       <x:c r="R24" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C60490.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C274877.html</x:v>
       </x:c>
       <x:c r="S24" s="7" t="str">
-        <x:v>Package: 0402; Power(Watts): 62.5mW; Resistance: 10kΩ; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 6.8kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
       </x:c>
       <x:c r="T24" s="7" t="str">
-        <x:v>Designators: R7, R16, R17, R18, R27, R28, R29, R30, R59, R60, R61, R71, R72, R73, R77, R78, R91, R92, R93, R99</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R13,R47; BOM_PASTER_8984112A_Y185.xls: R17</x:v>
       </x:c>
       <x:c r="U24" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V24" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
       <x:c r="W24" s="7" t="str">
         <x:v>Resistors</x:v>
@@ -6043,42 +6119,42 @@
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
       <x:c r="A25" s="7" t="str">
-        <x:v>C60491</x:v>
+        <x:v>C327379</x:v>
       </x:c>
       <x:c r="B25" s="7" t="str">
-        <x:v>RC0402FR-07100KL</x:v>
+        <x:v>RC0201FR-078K06L</x:v>
       </x:c>
       <x:c r="C25" s="7" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>YAGEO(国巨)</x:v>
       </x:c>
       <x:c r="D25" s="7" t="str">
-        <x:v>100kΩ 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>8.06k 1% 0201 chip resistor</x:v>
       </x:c>
       <x:c r="E25" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F25" s="7" t="str">
-        <x:v>RC0402FR-07100KL</x:v>
+        <x:v>RC0201FR-078K06L</x:v>
       </x:c>
       <x:c r="G25" s="7" t="str">
-        <x:v>R0402</x:v>
+        <x:v>R_0201_0603Metric</x:v>
       </x:c>
       <x:c r="H25" s="7" t="str">
-        <x:v>100kΩ</x:v>
+        <x:v>8.06k</x:v>
       </x:c>
       <x:c r="I25" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J25" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C60491</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20250610/89E4D743C004A82A45145C7A2CC3A578.pdf</x:v>
       </x:c>
       <x:c r="K25" s="7" t="str"/>
       <x:c r="L25" s="7" t="str"/>
       <x:c r="M25" s="7" t="str">
-        <x:v>../datasheets/C60491/RC0402FR-07100KL.pdf</x:v>
+        <x:v>../datasheets/C327379/RC0201FR-078K06L.pdf</x:v>
       </x:c>
       <x:c r="N25" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0402_L1.0-W0.5-H0.4.wrl</x:v>
+        <x:v>${KICAD10_3DMODEL_DIR}/Resistor_SMD.3dshapes/R_0201_0603Metric.step</x:v>
       </x:c>
       <x:c r="O25" s="7" t="str">
         <x:v>Active</x:v>
@@ -6087,22 +6163,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q25" s="7" t="str">
-        <x:v>RC0402FR-07100KL</x:v>
+        <x:v>R0201</x:v>
       </x:c>
       <x:c r="R25" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C60491.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C327379.html</x:v>
       </x:c>
       <x:c r="S25" s="7" t="str">
-        <x:v>Package: 0402; Resistance: 100kΩ; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0201; Resistance: 8.06k; Tolerance: 1%</x:v>
       </x:c>
       <x:c r="T25" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R14,R19; BOM_PASTER_8984112A_Y185.xls: R19</x:v>
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designators R6/R7/R8/R14/R15/R16.</x:v>
       </x:c>
       <x:c r="U25" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V25" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809; legacy_import</x:v>
+        <x:v>EBOM_V1.10</x:v>
       </x:c>
       <x:c r="W25" s="7" t="str">
         <x:v>Resistors</x:v>
@@ -6119,66 +6195,66 @@
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
       <x:c r="A26" s="7" t="str">
-        <x:v>C723375</x:v>
+        <x:v>C474825</x:v>
       </x:c>
       <x:c r="B26" s="7" t="str">
-        <x:v>PA2512FKF7T0R003E</x:v>
+        <x:v>RC0201FR-0776K8L</x:v>
       </x:c>
       <x:c r="C26" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D26" s="7" t="str">
-        <x:v>3mΩ ±1% 3W Current Sense Resistor</x:v>
+        <x:v>50mW 76.8kΩ 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E26" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F26" s="7" t="str">
-        <x:v>PA2512FKF7T0R003E</x:v>
+        <x:v>RC0201FR-0776K8L</x:v>
       </x:c>
       <x:c r="G26" s="7" t="str">
-        <x:v>R2512</x:v>
+        <x:v>R_0201_0603Metric</x:v>
       </x:c>
       <x:c r="H26" s="7" t="str">
-        <x:v>3mΩ</x:v>
+        <x:v>76.8kΩ</x:v>
       </x:c>
       <x:c r="I26" s="7" t="str">
-        <x:v>2512</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J26" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/5b6b15592a49e0e574b8071c20ab494b.pdf?productCode=C723375</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C474825</x:v>
       </x:c>
       <x:c r="K26" s="7" t="str"/>
       <x:c r="L26" s="7" t="str"/>
       <x:c r="M26" s="7" t="str">
-        <x:v>../datasheets/C723375/PA2512FKF7T0R003E.pdf</x:v>
+        <x:v>../datasheets/C474825/RC0201FR-0776K8L.pdf</x:v>
       </x:c>
       <x:c r="N26" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R2512_L6.3-W3.2-H0.6.wrl</x:v>
+        <x:v>${KICAD10_3DMODEL_DIR}/Resistor_SMD.3dshapes/R_0201_0603Metric.step</x:v>
       </x:c>
       <x:c r="O26" s="7" t="str">
-        <x:v>Active</x:v>
+        <x:v>OutOfStock</x:v>
       </x:c>
       <x:c r="P26" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q26" s="7" t="str">
-        <x:v>R2512</x:v>
+        <x:v>RC0201FR-0776K8L</x:v>
       </x:c>
       <x:c r="R26" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C723375.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C474825.html</x:v>
       </x:c>
       <x:c r="S26" s="7" t="str">
-        <x:v>Package: 2512; Power(Watts): 3W; Resistance: 3mΩ; Voltage Rating: -; Type: Current Sense Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 76.8kΩ; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
       </x:c>
       <x:c r="T26" s="7" t="str">
-        <x:v>Designators: R62, R63, R64</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R17</x:v>
       </x:c>
       <x:c r="U26" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V26" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
       <x:c r="W26" s="7" t="str">
         <x:v>Resistors</x:v>
@@ -6195,42 +6271,42 @@
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
       <x:c r="A27" s="7" t="str">
-        <x:v>C77623</x:v>
+        <x:v>C60490</x:v>
       </x:c>
       <x:c r="B27" s="7" t="str">
-        <x:v>RC0201FR-07100RL</x:v>
+        <x:v>RC0402FR-0710KL</x:v>
       </x:c>
       <x:c r="C27" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D27" s="7" t="str">
-        <x:v>50mW 100Ω 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>62.5mW 10kΩ 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E27" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F27" s="7" t="str">
-        <x:v>RC0201FR-07100RL</x:v>
+        <x:v>RC0402FR-0710KL</x:v>
       </x:c>
       <x:c r="G27" s="7" t="str">
-        <x:v>R_0201_0603Metric</x:v>
+        <x:v>R0402</x:v>
       </x:c>
       <x:c r="H27" s="7" t="str">
-        <x:v>100Ω</x:v>
+        <x:v>10kΩ</x:v>
       </x:c>
       <x:c r="I27" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J27" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C77623</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C60490</x:v>
       </x:c>
       <x:c r="K27" s="7" t="str"/>
       <x:c r="L27" s="7" t="str"/>
       <x:c r="M27" s="7" t="str">
-        <x:v>../datasheets/C77623/RC0201FR-07100RL.pdf</x:v>
+        <x:v>../datasheets/C60490/RC0402FR-0710KL.pdf</x:v>
       </x:c>
       <x:c r="N27" s="7" t="str">
-        <x:v>${KICAD10_3DMODEL_DIR}/Resistor_SMD.3dshapes/R_0201_0603Metric.step</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0402_L1.0-W0.5-H0.4.wrl</x:v>
       </x:c>
       <x:c r="O27" s="7" t="str">
         <x:v>Active</x:v>
@@ -6239,22 +6315,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q27" s="7" t="str">
-        <x:v>RC0201FR-07100RL</x:v>
+        <x:v>R0402</x:v>
       </x:c>
       <x:c r="R27" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C77623.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C60490.html</x:v>
       </x:c>
       <x:c r="S27" s="7" t="str">
-        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 100Ω; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 0402; Power(Watts): 62.5mW; Resistance: 10kΩ; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T27" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls, BOM_PASTER_8984112A_Y189.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R9,R10,R11,R23,R24,R25,R26,R27,R28,R29,R30,R31,R34,R38,R40,R42; BOM_PASTER_8984112A_Y185.xls: R5,R6,R13,R14,R15; BOM_PASTER_8984112A_Y189.xls: R3</x:v>
+        <x:v>Designators: R7, R16, R17, R18, R27, R28, R29, R30, R59, R60, R61, R71, R72, R73, R77, R78, R91, R92, R93, R99</x:v>
       </x:c>
       <x:c r="U27" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V27" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
       <x:c r="W27" s="7" t="str">
         <x:v>Resistors</x:v>
@@ -6271,42 +6347,42 @@
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
       <x:c r="A28" s="7" t="str">
-        <x:v>C82868</x:v>
+        <x:v>C60491</x:v>
       </x:c>
       <x:c r="B28" s="7" t="str">
-        <x:v>RC0402FR-0722KL</x:v>
+        <x:v>RC0402FR-07100KL</x:v>
       </x:c>
       <x:c r="C28" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D28" s="7" t="str">
-        <x:v>62.5mW 22kΩ 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>100kΩ 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E28" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F28" s="7" t="str">
-        <x:v>RC0402FR-0722KL</x:v>
+        <x:v>RC0402FR-07100KL</x:v>
       </x:c>
       <x:c r="G28" s="7" t="str">
-        <x:v>R_0402_1005Metric</x:v>
+        <x:v>R0402</x:v>
       </x:c>
       <x:c r="H28" s="7" t="str">
-        <x:v>22kΩ</x:v>
+        <x:v>100kΩ</x:v>
       </x:c>
       <x:c r="I28" s="7" t="str">
         <x:v>0402</x:v>
       </x:c>
       <x:c r="J28" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C82868</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C60491</x:v>
       </x:c>
       <x:c r="K28" s="7" t="str"/>
       <x:c r="L28" s="7" t="str"/>
       <x:c r="M28" s="7" t="str">
-        <x:v>../datasheets/C82868/RC0402FR-0722KL.pdf</x:v>
+        <x:v>../datasheets/C60491/RC0402FR-07100KL.pdf</x:v>
       </x:c>
       <x:c r="N28" s="7" t="str">
-        <x:v>${KICAD10_3DMODEL_DIR}/Resistor_SMD.3dshapes/R_0402_1005Metric.step</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R0402_L1.0-W0.5-H0.4.wrl</x:v>
       </x:c>
       <x:c r="O28" s="7" t="str">
         <x:v>Active</x:v>
@@ -6315,16 +6391,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q28" s="7" t="str">
-        <x:v>RC0402FR-0722KL</x:v>
+        <x:v>RC0402FR-07100KL</x:v>
       </x:c>
       <x:c r="R28" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C82868.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C60491.html</x:v>
       </x:c>
       <x:c r="S28" s="7" t="str">
-        <x:v>Package: 0402; Power(Watts): 62.5mW; Resistance: 22kΩ; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0402; Resistance: 100kΩ; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T28" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R1,R3,R4</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R14,R19; BOM_PASTER_8984112A_Y185.xls: R19</x:v>
       </x:c>
       <x:c r="U28" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -6347,42 +6423,42 @@
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
       <x:c r="A29" s="7" t="str">
-        <x:v>C851693</x:v>
+        <x:v>C723375</x:v>
       </x:c>
       <x:c r="B29" s="7" t="str">
-        <x:v>RC0201DR-0726K1L</x:v>
+        <x:v>PA2512FKF7T0R003E</x:v>
       </x:c>
       <x:c r="C29" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D29" s="7" t="str">
-        <x:v>26.1kΩ 50mW 25V Thick Film Resistor ±0.5% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>3mΩ ±1% 3W Current Sense Resistor</x:v>
       </x:c>
       <x:c r="E29" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F29" s="7" t="str">
-        <x:v>RC0201DR-0726K1L</x:v>
+        <x:v>PA2512FKF7T0R003E</x:v>
       </x:c>
       <x:c r="G29" s="7" t="str">
-        <x:v>R_0201_0603Metric</x:v>
+        <x:v>R2512</x:v>
       </x:c>
       <x:c r="H29" s="7" t="str">
-        <x:v>26.1kΩ</x:v>
+        <x:v>3mΩ</x:v>
       </x:c>
       <x:c r="I29" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>2512</x:v>
       </x:c>
       <x:c r="J29" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C851693</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/5b6b15592a49e0e574b8071c20ab494b.pdf?productCode=C723375</x:v>
       </x:c>
       <x:c r="K29" s="7" t="str"/>
       <x:c r="L29" s="7" t="str"/>
       <x:c r="M29" s="7" t="str">
-        <x:v>../datasheets/C851693/RC0201DR-0726K1L.pdf</x:v>
+        <x:v>../datasheets/C723375/PA2512FKF7T0R003E.pdf</x:v>
       </x:c>
       <x:c r="N29" s="7" t="str">
-        <x:v>${KICAD10_3DMODEL_DIR}/Resistor_SMD.3dshapes/R_0201_0603Metric.step</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Resistors/Resistors.3dshapes/R2512_L6.3-W3.2-H0.6.wrl</x:v>
       </x:c>
       <x:c r="O29" s="7" t="str">
         <x:v>Active</x:v>
@@ -6391,22 +6467,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q29" s="7" t="str">
-        <x:v>RC0201DR-0726K1L</x:v>
+        <x:v>R2512</x:v>
       </x:c>
       <x:c r="R29" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C851693.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C723375.html</x:v>
       </x:c>
       <x:c r="S29" s="7" t="str">
-        <x:v>Package: 0201; Resistance: 26.1kΩ; Power(Watts): 50mW; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±0.5%; Temperature Coefficient: ±200ppm/℃</x:v>
+        <x:v>Package: 2512; Power(Watts): 3W; Resistance: 3mΩ; Voltage Rating: -; Type: Current Sense Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T29" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R16</x:v>
+        <x:v>Designators: R62, R63, R64</x:v>
       </x:c>
       <x:c r="U29" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V29" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
       <x:c r="W29" s="7" t="str">
         <x:v>Resistors</x:v>
@@ -6423,42 +6499,42 @@
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
       <x:c r="A30" s="7" t="str">
-        <x:v>C93940</x:v>
+        <x:v>C77623</x:v>
       </x:c>
       <x:c r="B30" s="7" t="str">
-        <x:v>RC0402FR-076K8L</x:v>
+        <x:v>RC0201FR-07100RL</x:v>
       </x:c>
       <x:c r="C30" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D30" s="7" t="str">
-        <x:v>62.5mW 6.8kΩ 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>50mW 100Ω 25V Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E30" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F30" s="7" t="str">
-        <x:v>RC0402FR-076K8L</x:v>
+        <x:v>RC0201FR-07100RL</x:v>
       </x:c>
       <x:c r="G30" s="7" t="str">
-        <x:v>R_0402_1005Metric</x:v>
+        <x:v>R_0201_0603Metric</x:v>
       </x:c>
       <x:c r="H30" s="7" t="str">
-        <x:v>6.8kΩ</x:v>
+        <x:v>100Ω</x:v>
       </x:c>
       <x:c r="I30" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J30" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C93940</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C77623</x:v>
       </x:c>
       <x:c r="K30" s="7" t="str"/>
       <x:c r="L30" s="7" t="str"/>
       <x:c r="M30" s="7" t="str">
-        <x:v>../datasheets/C93940/RC0402FR-076K8L.pdf</x:v>
+        <x:v>../datasheets/C77623/RC0201FR-07100RL.pdf</x:v>
       </x:c>
       <x:c r="N30" s="7" t="str">
-        <x:v>${KICAD10_3DMODEL_DIR}/Resistor_SMD.3dshapes/R_0402_1005Metric.step</x:v>
+        <x:v>${KICAD10_3DMODEL_DIR}/Resistor_SMD.3dshapes/R_0201_0603Metric.step</x:v>
       </x:c>
       <x:c r="O30" s="7" t="str">
         <x:v>Active</x:v>
@@ -6467,22 +6543,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q30" s="7" t="str">
-        <x:v>R0402</x:v>
+        <x:v>RC0201FR-07100RL</x:v>
       </x:c>
       <x:c r="R30" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C93940.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C77623.html</x:v>
       </x:c>
       <x:c r="S30" s="7" t="str">
-        <x:v>Package: 0402; Power(Watts): 62.5mW; Resistance: 6.8kΩ; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0201; Power(Watts): 50mW; Resistance: 100Ω; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±1%; Temperature Coefficient: ±200ppm/℃</x:v>
       </x:c>
       <x:c r="T30" s="7" t="str">
-        <x:v>Designators: R76, R79, R80</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls, BOM_PASTER_8984112A_Y189.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R9,R10,R11,R23,R24,R25,R26,R27,R28,R29,R30,R31,R34,R38,R40,R42; BOM_PASTER_8984112A_Y185.xls: R5,R6,R13,R14,R15; BOM_PASTER_8984112A_Y189.xls: R3</x:v>
       </x:c>
       <x:c r="U30" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V30" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
       <x:c r="W30" s="7" t="str">
         <x:v>Resistors</x:v>
@@ -6499,39 +6575,39 @@
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
       <x:c r="A31" s="7" t="str">
-        <x:v>C93942</x:v>
+        <x:v>C82868</x:v>
       </x:c>
       <x:c r="B31" s="7" t="str">
-        <x:v>RC0402FR-0720KL</x:v>
+        <x:v>RC0402FR-0722KL</x:v>
       </x:c>
       <x:c r="C31" s="7" t="str">
         <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D31" s="7" t="str">
-        <x:v>20kΩ 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+        <x:v>62.5mW 22kΩ 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
       </x:c>
       <x:c r="E31" s="7" t="str">
         <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
       </x:c>
       <x:c r="F31" s="7" t="str">
-        <x:v>RC0402FR-0720KL</x:v>
+        <x:v>RC0402FR-0722KL</x:v>
       </x:c>
       <x:c r="G31" s="7" t="str">
         <x:v>R_0402_1005Metric</x:v>
       </x:c>
       <x:c r="H31" s="7" t="str">
-        <x:v>20kΩ</x:v>
+        <x:v>22kΩ</x:v>
       </x:c>
       <x:c r="I31" s="7" t="str">
         <x:v>0402</x:v>
       </x:c>
       <x:c r="J31" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C93942</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C82868</x:v>
       </x:c>
       <x:c r="K31" s="7" t="str"/>
       <x:c r="L31" s="7" t="str"/>
       <x:c r="M31" s="7" t="str">
-        <x:v>../datasheets/C93942/RC0402FR-0720KL.pdf</x:v>
+        <x:v>../datasheets/C82868/RC0402FR-0722KL.pdf</x:v>
       </x:c>
       <x:c r="N31" s="7" t="str">
         <x:v>${KICAD10_3DMODEL_DIR}/Resistor_SMD.3dshapes/R_0402_1005Metric.step</x:v>
@@ -6543,22 +6619,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q31" s="7" t="str">
-        <x:v>R0402</x:v>
+        <x:v>RC0402FR-0722KL</x:v>
       </x:c>
       <x:c r="R31" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C93942.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C82868.html</x:v>
       </x:c>
       <x:c r="S31" s="7" t="str">
-        <x:v>Package: 0402; Resistance: 20kΩ; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+        <x:v>Package: 0402; Power(Watts): 62.5mW; Resistance: 22kΩ; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
       </x:c>
       <x:c r="T31" s="7" t="str">
-        <x:v>Designators: R75</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R1,R3,R4</x:v>
       </x:c>
       <x:c r="U31" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V31" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809; legacy_import</x:v>
       </x:c>
       <x:c r="W31" s="7" t="str">
         <x:v>Resistors</x:v>
@@ -6573,16 +6649,244 @@
         <x:v>CONVERTED</x:v>
       </x:c>
     </x:row>
+    <x:row r="32" ht="24" customHeight="1">
+      <x:c r="A32" s="7" t="str">
+        <x:v>C851693</x:v>
+      </x:c>
+      <x:c r="B32" s="7" t="str">
+        <x:v>RC0201DR-0726K1L</x:v>
+      </x:c>
+      <x:c r="C32" s="7" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D32" s="7" t="str">
+        <x:v>26.1kΩ 50mW 25V Thick Film Resistor ±0.5% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</x:v>
+      </x:c>
+      <x:c r="E32" s="7" t="str">
+        <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
+      </x:c>
+      <x:c r="F32" s="7" t="str">
+        <x:v>RC0201DR-0726K1L</x:v>
+      </x:c>
+      <x:c r="G32" s="7" t="str">
+        <x:v>R_0201_0603Metric</x:v>
+      </x:c>
+      <x:c r="H32" s="7" t="str">
+        <x:v>26.1kΩ</x:v>
+      </x:c>
+      <x:c r="I32" s="7" t="str">
+        <x:v>0201</x:v>
+      </x:c>
+      <x:c r="J32" s="7" t="str">
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C851693</x:v>
+      </x:c>
+      <x:c r="K32" s="7" t="str"/>
+      <x:c r="L32" s="7" t="str"/>
+      <x:c r="M32" s="7" t="str">
+        <x:v>../datasheets/C851693/RC0201DR-0726K1L.pdf</x:v>
+      </x:c>
+      <x:c r="N32" s="7" t="str">
+        <x:v>${KICAD10_3DMODEL_DIR}/Resistor_SMD.3dshapes/R_0201_0603Metric.step</x:v>
+      </x:c>
+      <x:c r="O32" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P32" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q32" s="7" t="str">
+        <x:v>RC0201DR-0726K1L</x:v>
+      </x:c>
+      <x:c r="R32" s="7" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C851693.html</x:v>
+      </x:c>
+      <x:c r="S32" s="7" t="str">
+        <x:v>Package: 0201; Resistance: 26.1kΩ; Power(Watts): 50mW; Voltage Rating: 25V; Operating Temperature: -55℃~+125℃; Type: Thick Film Resistor; Tolerance: ±0.5%; Temperature Coefficient: ±200ppm/℃</x:v>
+      </x:c>
+      <x:c r="T32" s="7" t="str">
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: R16</x:v>
+      </x:c>
+      <x:c r="U32" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V32" s="7" t="str">
+        <x:v>legacy_import</x:v>
+      </x:c>
+      <x:c r="W32" s="7" t="str">
+        <x:v>Resistors</x:v>
+      </x:c>
+      <x:c r="X32" s="7" t="str">
+        <x:v>Resistors.kicad_sym</x:v>
+      </x:c>
+      <x:c r="Y32" s="7" t="str">
+        <x:v>Resistors.pretty</x:v>
+      </x:c>
+      <x:c r="Z32" s="7" t="str">
+        <x:v>CONVERTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="24" customHeight="1">
+      <x:c r="A33" s="7" t="str">
+        <x:v>C93940</x:v>
+      </x:c>
+      <x:c r="B33" s="7" t="str">
+        <x:v>RC0402FR-076K8L</x:v>
+      </x:c>
+      <x:c r="C33" s="7" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D33" s="7" t="str">
+        <x:v>62.5mW 6.8kΩ 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+      </x:c>
+      <x:c r="E33" s="7" t="str">
+        <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
+      </x:c>
+      <x:c r="F33" s="7" t="str">
+        <x:v>RC0402FR-076K8L</x:v>
+      </x:c>
+      <x:c r="G33" s="7" t="str">
+        <x:v>R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="H33" s="7" t="str">
+        <x:v>6.8kΩ</x:v>
+      </x:c>
+      <x:c r="I33" s="7" t="str">
+        <x:v>0402</x:v>
+      </x:c>
+      <x:c r="J33" s="7" t="str">
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C93940</x:v>
+      </x:c>
+      <x:c r="K33" s="7" t="str"/>
+      <x:c r="L33" s="7" t="str"/>
+      <x:c r="M33" s="7" t="str">
+        <x:v>../datasheets/C93940/RC0402FR-076K8L.pdf</x:v>
+      </x:c>
+      <x:c r="N33" s="7" t="str">
+        <x:v>${KICAD10_3DMODEL_DIR}/Resistor_SMD.3dshapes/R_0402_1005Metric.step</x:v>
+      </x:c>
+      <x:c r="O33" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P33" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q33" s="7" t="str">
+        <x:v>R0402</x:v>
+      </x:c>
+      <x:c r="R33" s="7" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C93940.html</x:v>
+      </x:c>
+      <x:c r="S33" s="7" t="str">
+        <x:v>Package: 0402; Power(Watts): 62.5mW; Resistance: 6.8kΩ; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+      </x:c>
+      <x:c r="T33" s="7" t="str">
+        <x:v>Designators: R76, R79, R80</x:v>
+      </x:c>
+      <x:c r="U33" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V33" s="7" t="str">
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+      </x:c>
+      <x:c r="W33" s="7" t="str">
+        <x:v>Resistors</x:v>
+      </x:c>
+      <x:c r="X33" s="7" t="str">
+        <x:v>Resistors.kicad_sym</x:v>
+      </x:c>
+      <x:c r="Y33" s="7" t="str">
+        <x:v>Resistors.pretty</x:v>
+      </x:c>
+      <x:c r="Z33" s="7" t="str">
+        <x:v>CONVERTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="24" customHeight="1">
+      <x:c r="A34" s="7" t="str">
+        <x:v>C93942</x:v>
+      </x:c>
+      <x:c r="B34" s="7" t="str">
+        <x:v>RC0402FR-0720KL</x:v>
+      </x:c>
+      <x:c r="C34" s="7" t="str">
+        <x:v>YAGEO</x:v>
+      </x:c>
+      <x:c r="D34" s="7" t="str">
+        <x:v>20kΩ 62.5mW 50V Thick Film Resistor ±100ppm/℃ ±1% 0402 Chip Resistor - Surface Mount RoHS</x:v>
+      </x:c>
+      <x:c r="E34" s="7" t="str">
+        <x:v>Resistors/Chip Resistor - Surface Mount</x:v>
+      </x:c>
+      <x:c r="F34" s="7" t="str">
+        <x:v>RC0402FR-0720KL</x:v>
+      </x:c>
+      <x:c r="G34" s="7" t="str">
+        <x:v>R_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="H34" s="7" t="str">
+        <x:v>20kΩ</x:v>
+      </x:c>
+      <x:c r="I34" s="7" t="str">
+        <x:v>0402</x:v>
+      </x:c>
+      <x:c r="J34" s="7" t="str">
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/b426be3ce22c6de3e0c3a2248e49159e.pdf?productCode=C93942</x:v>
+      </x:c>
+      <x:c r="K34" s="7" t="str"/>
+      <x:c r="L34" s="7" t="str"/>
+      <x:c r="M34" s="7" t="str">
+        <x:v>../datasheets/C93942/RC0402FR-0720KL.pdf</x:v>
+      </x:c>
+      <x:c r="N34" s="7" t="str">
+        <x:v>${KICAD10_3DMODEL_DIR}/Resistor_SMD.3dshapes/R_0402_1005Metric.step</x:v>
+      </x:c>
+      <x:c r="O34" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P34" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q34" s="7" t="str">
+        <x:v>R0402</x:v>
+      </x:c>
+      <x:c r="R34" s="7" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C93942.html</x:v>
+      </x:c>
+      <x:c r="S34" s="7" t="str">
+        <x:v>Package: 0402; Resistance: 20kΩ; Power(Watts): 62.5mW; Voltage Rating: 50V; Operating Temperature: -55℃~+155℃; Type: Thick Film Resistor; Temperature Coefficient: ±100ppm/℃; Tolerance: ±1%</x:v>
+      </x:c>
+      <x:c r="T34" s="7" t="str">
+        <x:v>Designators: R75</x:v>
+      </x:c>
+      <x:c r="U34" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V34" s="7" t="str">
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+      </x:c>
+      <x:c r="W34" s="7" t="str">
+        <x:v>Resistors</x:v>
+      </x:c>
+      <x:c r="X34" s="7" t="str">
+        <x:v>Resistors.kicad_sym</x:v>
+      </x:c>
+      <x:c r="Y34" s="7" t="str">
+        <x:v>Resistors.pretty</x:v>
+      </x:c>
+      <x:c r="Z34" s="7" t="str">
+        <x:v>CONVERTED</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="U5:U31">
+  <x:conditionalFormatting sqref="U5:U34">
     <x:cfRule type="containsText" dxfId="30" priority="1" operator="containsText" text="CLASSIFIED_PARTIAL"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="Z5:Z31">
+  <x:conditionalFormatting sqref="Z5:Z34">
     <x:cfRule type="containsText" dxfId="31" priority="2" operator="containsText" text="PENDING_CONVERSION"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8161c44767984191"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf41ef0b2dc5c4753"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6794,7 +7098,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08322b5dabc04353"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8438a5996bb74744"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7006,7 +7310,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fba03f46dec49f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd02bcc6c57194fb1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7050,7 +7354,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="str">
-        <x:v>类别：Capacitors；记录数：27；来源：library_index.csv</x:v>
+        <x:v>类别：Capacitors；记录数：31；来源：library_index.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -7819,42 +8123,42 @@
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>C3039698</x:v>
+        <x:v>C29936</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>CL10B106MQ8NRNC</x:v>
+        <x:v>CL10B105KA8NNNC</x:v>
       </x:c>
       <x:c r="C14" s="7" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>SAMSUNG(三星)</x:v>
       </x:c>
       <x:c r="D14" s="7" t="str">
-        <x:v>10uF ±20% 6.3V Ceramic Capacitor X7R 0603</x:v>
+        <x:v>1uF 25V X7R 0603 ceramic capacitor</x:v>
       </x:c>
       <x:c r="E14" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F14" s="7" t="str">
-        <x:v>CL10B106MQ8NRNC</x:v>
+        <x:v>CL10B105KA8NNNC</x:v>
       </x:c>
       <x:c r="G14" s="7" t="str">
-        <x:v>C0603</x:v>
+        <x:v>C_0603_1608Metric</x:v>
       </x:c>
       <x:c r="H14" s="7" t="str">
-        <x:v>10uF</x:v>
+        <x:v>1uF</x:v>
       </x:c>
       <x:c r="I14" s="7" t="str">
         <x:v>0603</x:v>
       </x:c>
       <x:c r="J14" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/25aeaed41ae8f3c7d2a7fa32796a6299.pdf?productCode=C3039698</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20160218/1457707763339.pdf</x:v>
       </x:c>
       <x:c r="K14" s="7" t="str"/>
       <x:c r="L14" s="7" t="str"/>
       <x:c r="M14" s="7" t="str">
-        <x:v>../datasheets/C3039698/CL10B106MQ8NRNC.pdf</x:v>
+        <x:v>../datasheets/C29936/CL10B105KA8NNNC.pdf</x:v>
       </x:c>
       <x:c r="N14" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0603_L1.6-W0.8-H0.8.wrl</x:v>
+        <x:v>${KICAD10_3DMODEL_DIR}/Capacitor_SMD.3dshapes/C_0603_1608Metric.step</x:v>
       </x:c>
       <x:c r="O14" s="7" t="str">
         <x:v>Active</x:v>
@@ -7863,22 +8167,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str">
-        <x:v>0603-10uF-6.3V-20%</x:v>
+        <x:v>C0603</x:v>
       </x:c>
       <x:c r="R14" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C3039698.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C29936.html</x:v>
       </x:c>
       <x:c r="S14" s="7" t="str">
-        <x:v>Package: 0603; Capacitance: 10uF; Temperature Coefficient: X7R; Tolerance: ±20%; Voltage Rating: 6.3V</x:v>
+        <x:v>Package: 0603; Capacitance: 1uF; Voltage: 25V; Tolerance: 10%; Temperature Coefficient: X7R</x:v>
       </x:c>
       <x:c r="T14" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C20</x:v>
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designators C11/C13/C21.</x:v>
       </x:c>
       <x:c r="U14" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V14" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>EBOM_V1.10</x:v>
       </x:c>
       <x:c r="W14" s="7" t="str">
         <x:v>Capacitors</x:v>
@@ -7895,42 +8199,42 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>C307331</x:v>
+        <x:v>C3039698</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>CL05B104KB54PNC</x:v>
+        <x:v>CL10B106MQ8NRNC</x:v>
       </x:c>
       <x:c r="C15" s="7" t="str">
-        <x:v>SAMSUNG</x:v>
+        <x:v>Samsung Electro-Mechanics</x:v>
       </x:c>
       <x:c r="D15" s="7" t="str">
-        <x:v>100nF ±10% 50V Ceramic Capacitor X7R</x:v>
+        <x:v>10uF ±20% 6.3V Ceramic Capacitor X7R 0603</x:v>
       </x:c>
       <x:c r="E15" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F15" s="7" t="str">
-        <x:v>CL05B104KB54PNC</x:v>
+        <x:v>CL10B106MQ8NRNC</x:v>
       </x:c>
       <x:c r="G15" s="7" t="str">
-        <x:v>C0402</x:v>
+        <x:v>C0603</x:v>
       </x:c>
       <x:c r="H15" s="7" t="str">
-        <x:v>100nF</x:v>
+        <x:v>10uF</x:v>
       </x:c>
       <x:c r="I15" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>0603</x:v>
       </x:c>
       <x:c r="J15" s="7" t="str">
-        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20160218/1457707763339.pdf</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/25aeaed41ae8f3c7d2a7fa32796a6299.pdf?productCode=C3039698</x:v>
       </x:c>
       <x:c r="K15" s="7" t="str"/>
       <x:c r="L15" s="7" t="str"/>
       <x:c r="M15" s="7" t="str">
-        <x:v>../datasheets/C307331/CL05B104KB54PNC.pdf</x:v>
+        <x:v>../datasheets/C3039698/CL10B106MQ8NRNC.pdf</x:v>
       </x:c>
       <x:c r="N15" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0402_L1.0-W0.5-H0.5.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0603_L1.6-W0.8-H0.8.wrl</x:v>
       </x:c>
       <x:c r="O15" s="7" t="str">
         <x:v>Active</x:v>
@@ -7939,22 +8243,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q15" s="7" t="str">
-        <x:v>0402-100nF-50V-10%</x:v>
+        <x:v>0603-10uF-6.3V-20%</x:v>
       </x:c>
       <x:c r="R15" s="7" t="str">
-        <x:v>https://item.szlcsc.com/291005.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C3039698.html</x:v>
       </x:c>
       <x:c r="S15" s="7" t="str">
-        <x:v>Package: 0402; Capacitance: 100nF; Tolerance: ±10%; Voltage Rating: 50V; Temperature Coefficient: X7R</x:v>
+        <x:v>Package: 0603; Capacitance: 10uF; Temperature Coefficient: X7R; Tolerance: ±20%; Voltage Rating: 6.3V</x:v>
       </x:c>
       <x:c r="T15" s="7" t="str">
-        <x:v>Designators: Y43-C1,C3,C6,C9,C10,C12,C14,C15,C18</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C20</x:v>
       </x:c>
       <x:c r="U15" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V15" s="7" t="str">
-        <x:v>Y43</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
       <x:c r="W15" s="7" t="str">
         <x:v>Capacitors</x:v>
@@ -7971,42 +8275,42 @@
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>C329936</x:v>
+        <x:v>C307331</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>CGA4J1X7S1C106KT000N</x:v>
+        <x:v>CL05B104KB54PNC</x:v>
       </x:c>
       <x:c r="C16" s="7" t="str">
-        <x:v>TDK</x:v>
+        <x:v>SAMSUNG</x:v>
       </x:c>
       <x:c r="D16" s="7" t="str">
-        <x:v>10uF ±10% 16V Ceramic Capacitor X7S 0805</x:v>
+        <x:v>100nF ±10% 50V Ceramic Capacitor X7R</x:v>
       </x:c>
       <x:c r="E16" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F16" s="7" t="str">
-        <x:v>CGA4J1X7S1C106KT000N</x:v>
+        <x:v>CL05B104KB54PNC</x:v>
       </x:c>
       <x:c r="G16" s="7" t="str">
-        <x:v>C0805</x:v>
+        <x:v>C0402</x:v>
       </x:c>
       <x:c r="H16" s="7" t="str">
-        <x:v>10uF</x:v>
+        <x:v>100nF</x:v>
       </x:c>
       <x:c r="I16" s="7" t="str">
-        <x:v>0805</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J16" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/fb3179df2df2fa358ee13dff52d60ee7.pdf?productCode=C329936</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20160218/1457707763339.pdf</x:v>
       </x:c>
       <x:c r="K16" s="7" t="str"/>
       <x:c r="L16" s="7" t="str"/>
       <x:c r="M16" s="7" t="str">
-        <x:v>../datasheets/C329936/CGA4J1X7S1C106KT000N.pdf</x:v>
+        <x:v>../datasheets/C307331/CL05B104KB54PNC.pdf</x:v>
       </x:c>
       <x:c r="N16" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0805_L2.0-W1.3-H1.3.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0402_L1.0-W0.5-H0.5.wrl</x:v>
       </x:c>
       <x:c r="O16" s="7" t="str">
         <x:v>Active</x:v>
@@ -8015,22 +8319,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str">
-        <x:v>C0805</x:v>
+        <x:v>0402-100nF-50V-10%</x:v>
       </x:c>
       <x:c r="R16" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C329936.html</x:v>
+        <x:v>https://item.szlcsc.com/291005.html</x:v>
       </x:c>
       <x:c r="S16" s="7" t="str">
-        <x:v>Package: 0805; Capacitance: 10uF; Temperature Coefficient: X7S; Tolerance: ±10%; Voltage Rating: 16V</x:v>
+        <x:v>Package: 0402; Capacitance: 100nF; Tolerance: ±10%; Voltage Rating: 50V; Temperature Coefficient: X7R</x:v>
       </x:c>
       <x:c r="T16" s="7" t="str">
-        <x:v>Designators: C9, C11, C16, C21, C22, C79, C80</x:v>
+        <x:v>Designators: Y43-C1,C3,C6,C9,C10,C12,C14,C15,C18</x:v>
       </x:c>
       <x:c r="U16" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V16" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>Y43</x:v>
       </x:c>
       <x:c r="W16" s="7" t="str">
         <x:v>Capacitors</x:v>
@@ -8047,66 +8351,66 @@
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
       <x:c r="A17" s="7" t="str">
-        <x:v>C382253</x:v>
+        <x:v>C329936</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
-        <x:v>FM18X222K101PSG</x:v>
+        <x:v>CGA4J1X7S1C106KT000N</x:v>
       </x:c>
       <x:c r="C17" s="7" t="str">
-        <x:v>PSA</x:v>
+        <x:v>TDK</x:v>
       </x:c>
       <x:c r="D17" s="7" t="str">
-        <x:v>2.2nF ±10% 100V Ceramic Capacitor X7R 0603</x:v>
+        <x:v>10uF ±10% 16V Ceramic Capacitor X7S 0805</x:v>
       </x:c>
       <x:c r="E17" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F17" s="7" t="str">
-        <x:v>FM18X222K101PSG</x:v>
+        <x:v>CGA4J1X7S1C106KT000N</x:v>
       </x:c>
       <x:c r="G17" s="7" t="str">
-        <x:v>C0603</x:v>
+        <x:v>C0805</x:v>
       </x:c>
       <x:c r="H17" s="7" t="str">
-        <x:v>2.2nF</x:v>
+        <x:v>10uF</x:v>
       </x:c>
       <x:c r="I17" s="7" t="str">
-        <x:v>0603</x:v>
+        <x:v>0805</x:v>
       </x:c>
       <x:c r="J17" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/8aced6bf19551db75d1c722c291966af.pdf?productCode=C382253</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/fb3179df2df2fa358ee13dff52d60ee7.pdf?productCode=C329936</x:v>
       </x:c>
       <x:c r="K17" s="7" t="str"/>
       <x:c r="L17" s="7" t="str"/>
       <x:c r="M17" s="7" t="str">
-        <x:v>../datasheets/C382253/FM18X222K101PSG.pdf</x:v>
+        <x:v>../datasheets/C329936/CGA4J1X7S1C106KT000N.pdf</x:v>
       </x:c>
       <x:c r="N17" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0603_L1.6-W0.8-H0.8.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0805_L2.0-W1.3-H1.3.wrl</x:v>
       </x:c>
       <x:c r="O17" s="7" t="str">
-        <x:v>OutOfStock</x:v>
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="P17" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q17" s="7" t="str">
-        <x:v>0603-2.2nF-100V-10%</x:v>
+        <x:v>C0805</x:v>
       </x:c>
       <x:c r="R17" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C382253.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C329936.html</x:v>
       </x:c>
       <x:c r="S17" s="7" t="str">
-        <x:v>Package: 0603; Capacitance: 2.2nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 100V</x:v>
+        <x:v>Package: 0805; Capacitance: 10uF; Temperature Coefficient: X7S; Tolerance: ±10%; Voltage Rating: 16V</x:v>
       </x:c>
       <x:c r="T17" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C61,C62,C63</x:v>
+        <x:v>Designators: C9, C11, C16, C21, C22, C79, C80</x:v>
       </x:c>
       <x:c r="U17" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V17" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
       <x:c r="W17" s="7" t="str">
         <x:v>Capacitors</x:v>
@@ -8123,60 +8427,60 @@
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18" s="7" t="str">
-        <x:v>C5156756</x:v>
+        <x:v>C382253</x:v>
       </x:c>
       <x:c r="B18" s="7" t="str">
-        <x:v>FS32X106K101EGG</x:v>
+        <x:v>FM18X222K101PSG</x:v>
       </x:c>
       <x:c r="C18" s="7" t="str">
         <x:v>PSA</x:v>
       </x:c>
       <x:c r="D18" s="7" t="str">
-        <x:v>10uF ±10% 100V Ceramic Capacitor X7R 1210</x:v>
+        <x:v>2.2nF ±10% 100V Ceramic Capacitor X7R 0603</x:v>
       </x:c>
       <x:c r="E18" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F18" s="7" t="str">
-        <x:v>FS32X106K101EGG</x:v>
+        <x:v>FM18X222K101PSG</x:v>
       </x:c>
       <x:c r="G18" s="7" t="str">
-        <x:v>C1210</x:v>
+        <x:v>C0603</x:v>
       </x:c>
       <x:c r="H18" s="7" t="str">
-        <x:v>10uF</x:v>
+        <x:v>2.2nF</x:v>
       </x:c>
       <x:c r="I18" s="7" t="str">
-        <x:v>1210</x:v>
+        <x:v>0603</x:v>
       </x:c>
       <x:c r="J18" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/18a0c9f8bf4d73d021cc722eccd020e0.pdf?productCode=C5156756</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/8aced6bf19551db75d1c722c291966af.pdf?productCode=C382253</x:v>
       </x:c>
       <x:c r="K18" s="7" t="str"/>
       <x:c r="L18" s="7" t="str"/>
       <x:c r="M18" s="7" t="str">
-        <x:v>../datasheets/C5156756/FS32X106K101EGG.pdf</x:v>
+        <x:v>../datasheets/C382253/FM18X222K101PSG.pdf</x:v>
       </x:c>
       <x:c r="N18" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C1210_L3.2-W2.5-H2.5.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0603_L1.6-W0.8-H0.8.wrl</x:v>
       </x:c>
       <x:c r="O18" s="7" t="str">
-        <x:v>Active</x:v>
+        <x:v>OutOfStock</x:v>
       </x:c>
       <x:c r="P18" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q18" s="7" t="str">
-        <x:v>1210-10uF-100V-10%</x:v>
+        <x:v>0603-2.2nF-100V-10%</x:v>
       </x:c>
       <x:c r="R18" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C5156756.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C382253.html</x:v>
       </x:c>
       <x:c r="S18" s="7" t="str">
-        <x:v>Package: 1210; Capacitance: 10uF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 100V</x:v>
+        <x:v>Package: 0603; Capacitance: 2.2nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 100V</x:v>
       </x:c>
       <x:c r="T18" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C8,C16,C17,C22</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C61,C62,C63</x:v>
       </x:c>
       <x:c r="U18" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -8199,42 +8503,42 @@
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
       <x:c r="A19" s="7" t="str">
-        <x:v>C525226</x:v>
+        <x:v>C445740</x:v>
       </x:c>
       <x:c r="B19" s="7" t="str">
-        <x:v>FN15X104K500PKG</x:v>
+        <x:v>C1005X7S1A225KT000E</x:v>
       </x:c>
       <x:c r="C19" s="7" t="str">
-        <x:v>PSA</x:v>
+        <x:v>TDK</x:v>
       </x:c>
       <x:c r="D19" s="7" t="str">
-        <x:v>100nF ±10% 50V Ceramic Capacitor X7R 0402</x:v>
+        <x:v>2.2uF 10V X7S 0402 ceramic capacitor</x:v>
       </x:c>
       <x:c r="E19" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F19" s="7" t="str">
-        <x:v>FN15X104K500PKG</x:v>
+        <x:v>C1005X7S1A225KT000E</x:v>
       </x:c>
       <x:c r="G19" s="7" t="str">
-        <x:v>C0402</x:v>
+        <x:v>C_0402_1005Metric</x:v>
       </x:c>
       <x:c r="H19" s="7" t="str">
-        <x:v>100nF</x:v>
+        <x:v>2.2uF</x:v>
       </x:c>
       <x:c r="I19" s="7" t="str">
         <x:v>0402</x:v>
       </x:c>
       <x:c r="J19" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/3d771c0c586676719f80e96a0f8d9dcd.pdf?productCode=C525226</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20191108/C445765_930F403C9F9F1C91FA65B6959DB97EFA.pdf</x:v>
       </x:c>
       <x:c r="K19" s="7" t="str"/>
       <x:c r="L19" s="7" t="str"/>
       <x:c r="M19" s="7" t="str">
-        <x:v>../datasheets/C525226/FN15X104K500PKG.pdf</x:v>
+        <x:v>../datasheets/C445740/C1005X7S1A225KT000E.pdf</x:v>
       </x:c>
       <x:c r="N19" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0402_L1.0-W0.5-H0.5.wrl</x:v>
+        <x:v>${KICAD10_3DMODEL_DIR}/Capacitor_SMD.3dshapes/C_0402_1005Metric.step</x:v>
       </x:c>
       <x:c r="O19" s="7" t="str">
         <x:v>Active</x:v>
@@ -8243,22 +8547,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q19" s="7" t="str">
-        <x:v>0402-100nF-50V-10%</x:v>
+        <x:v>C0402</x:v>
       </x:c>
       <x:c r="R19" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C525226.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C445740.html</x:v>
       </x:c>
       <x:c r="S19" s="7" t="str">
-        <x:v>Package: 0402; Capacitance: 100nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 50V</x:v>
+        <x:v>Package: 0402; Capacitance: 2.2uF; Voltage: 10V; Tolerance: 10%; Temperature Coefficient: X7S</x:v>
       </x:c>
       <x:c r="T19" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C19; BOM_PASTER_8984112A_Y185.xls: C5</x:v>
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designator C19.</x:v>
       </x:c>
       <x:c r="U19" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V19" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>EBOM_V1.10</x:v>
       </x:c>
       <x:c r="W19" s="7" t="str">
         <x:v>Capacitors</x:v>
@@ -8275,42 +8579,42 @@
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="7" t="str">
-        <x:v>C527014</x:v>
+        <x:v>C5156756</x:v>
       </x:c>
       <x:c r="B20" s="7" t="str">
-        <x:v>CC0402KRX7R0BB103</x:v>
+        <x:v>FS32X106K101EGG</x:v>
       </x:c>
       <x:c r="C20" s="7" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>PSA</x:v>
       </x:c>
       <x:c r="D20" s="7" t="str">
-        <x:v>10nF ±10% 100V Ceramic Capacitor X7R 0402</x:v>
+        <x:v>10uF ±10% 100V Ceramic Capacitor X7R 1210</x:v>
       </x:c>
       <x:c r="E20" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F20" s="7" t="str">
-        <x:v>CC0402KRX7R0BB103</x:v>
+        <x:v>FS32X106K101EGG</x:v>
       </x:c>
       <x:c r="G20" s="7" t="str">
-        <x:v>C0402</x:v>
+        <x:v>C1210</x:v>
       </x:c>
       <x:c r="H20" s="7" t="str">
-        <x:v>10nF</x:v>
+        <x:v>10uF</x:v>
       </x:c>
       <x:c r="I20" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>1210</x:v>
       </x:c>
       <x:c r="J20" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/23ccee80ee542e7cf156a772bb589942.pdf?productCode=C527014</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/18a0c9f8bf4d73d021cc722eccd020e0.pdf?productCode=C5156756</x:v>
       </x:c>
       <x:c r="K20" s="7" t="str"/>
       <x:c r="L20" s="7" t="str"/>
       <x:c r="M20" s="7" t="str">
-        <x:v>../datasheets/C527014/CC0402KRX7R0BB103.pdf</x:v>
+        <x:v>../datasheets/C5156756/FS32X106K101EGG.pdf</x:v>
       </x:c>
       <x:c r="N20" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0402_L1.0-W0.5-H0.5.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C1210_L3.2-W2.5-H2.5.wrl</x:v>
       </x:c>
       <x:c r="O20" s="7" t="str">
         <x:v>Active</x:v>
@@ -8319,16 +8623,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q20" s="7" t="str">
-        <x:v>CC0402KRX7R0BB103</x:v>
+        <x:v>1210-10uF-100V-10%</x:v>
       </x:c>
       <x:c r="R20" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C527014.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C5156756.html</x:v>
       </x:c>
       <x:c r="S20" s="7" t="str">
-        <x:v>Package: 0402; Capacitance: 10nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 100V</x:v>
+        <x:v>Package: 1210; Capacitance: 10uF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 100V</x:v>
       </x:c>
       <x:c r="T20" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C52</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C8,C16,C17,C22</x:v>
       </x:c>
       <x:c r="U20" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -8351,39 +8655,39 @@
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
       <x:c r="A21" s="7" t="str">
-        <x:v>C52923</x:v>
+        <x:v>C525226</x:v>
       </x:c>
       <x:c r="B21" s="7" t="str">
-        <x:v>CL05A105KA5NQNC</x:v>
+        <x:v>FN15X104K500PKG</x:v>
       </x:c>
       <x:c r="C21" s="7" t="str">
-        <x:v>SAMSUNG</x:v>
+        <x:v>PSA</x:v>
       </x:c>
       <x:c r="D21" s="7" t="str">
-        <x:v>1uF ±10% 25V Ceramic Capacitor X5R</x:v>
+        <x:v>100nF ±10% 50V Ceramic Capacitor X7R 0402</x:v>
       </x:c>
       <x:c r="E21" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F21" s="7" t="str">
-        <x:v>CL05A105KA5NQNC</x:v>
+        <x:v>FN15X104K500PKG</x:v>
       </x:c>
       <x:c r="G21" s="7" t="str">
         <x:v>C0402</x:v>
       </x:c>
       <x:c r="H21" s="7" t="str">
-        <x:v>1uF</x:v>
+        <x:v>100nF</x:v>
       </x:c>
       <x:c r="I21" s="7" t="str">
         <x:v>0402</x:v>
       </x:c>
       <x:c r="J21" s="7" t="str">
-        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20160218/1457707763339.pdf</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/3d771c0c586676719f80e96a0f8d9dcd.pdf?productCode=C525226</x:v>
       </x:c>
       <x:c r="K21" s="7" t="str"/>
       <x:c r="L21" s="7" t="str"/>
       <x:c r="M21" s="7" t="str">
-        <x:v>../datasheets/C52923/CL05A105KA5NQNC.pdf</x:v>
+        <x:v>../datasheets/C525226/FN15X104K500PKG.pdf</x:v>
       </x:c>
       <x:c r="N21" s="7" t="str">
         <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0402_L1.0-W0.5-H0.5.wrl</x:v>
@@ -8395,22 +8699,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q21" s="7" t="str">
-        <x:v>0402-1uF-10V-10%</x:v>
+        <x:v>0402-100nF-50V-10%</x:v>
       </x:c>
       <x:c r="R21" s="7" t="str">
-        <x:v>https://item.szlcsc.com/53938.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C525226.html</x:v>
       </x:c>
       <x:c r="S21" s="7" t="str">
-        <x:v>Package: 0402; Capacitance: 1uF; Tolerance: ±10%; Voltage Rating: 25V; Temperature Coefficient: X5R</x:v>
+        <x:v>Package: 0402; Capacitance: 100nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 50V</x:v>
       </x:c>
       <x:c r="T21" s="7" t="str">
-        <x:v>Designators: Y43-C2,C4,C5,C7,C16</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C19; BOM_PASTER_8984112A_Y185.xls: C5</x:v>
       </x:c>
       <x:c r="U21" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V21" s="7" t="str">
-        <x:v>Y43</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
       <x:c r="W21" s="7" t="str">
         <x:v>Capacitors</x:v>
@@ -8427,60 +8731,60 @@
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
       <x:c r="A22" s="7" t="str">
-        <x:v>C561710</x:v>
+        <x:v>C527014</x:v>
       </x:c>
       <x:c r="B22" s="7" t="str">
-        <x:v>FN03N100J500PLG</x:v>
+        <x:v>CC0402KRX7R0BB103</x:v>
       </x:c>
       <x:c r="C22" s="7" t="str">
-        <x:v>PSA</x:v>
+        <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D22" s="7" t="str">
-        <x:v>10pF ±5% 50V Ceramic Capacitor C0G 0201</x:v>
+        <x:v>10nF ±10% 100V Ceramic Capacitor X7R 0402</x:v>
       </x:c>
       <x:c r="E22" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F22" s="7" t="str">
-        <x:v>FN03N100J500PLG</x:v>
+        <x:v>CC0402KRX7R0BB103</x:v>
       </x:c>
       <x:c r="G22" s="7" t="str">
-        <x:v>C_0201_0603Metric</x:v>
+        <x:v>C0402</x:v>
       </x:c>
       <x:c r="H22" s="7" t="str">
-        <x:v>10pF</x:v>
+        <x:v>10nF</x:v>
       </x:c>
       <x:c r="I22" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J22" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/1497a6a2cea2f2b0acf5e045d2bc193c.pdf?productCode=C561710</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/23ccee80ee542e7cf156a772bb589942.pdf?productCode=C527014</x:v>
       </x:c>
       <x:c r="K22" s="7" t="str"/>
       <x:c r="L22" s="7" t="str"/>
       <x:c r="M22" s="7" t="str">
-        <x:v>../datasheets/C561710/FN03N100J500PLG.pdf</x:v>
+        <x:v>../datasheets/C527014/CC0402KRX7R0BB103.pdf</x:v>
       </x:c>
       <x:c r="N22" s="7" t="str">
-        <x:v>${KICAD10_3DMODEL_DIR}/Capacitor_SMD.3dshapes/C_0201_0603Metric.step</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0402_L1.0-W0.5-H0.5.wrl</x:v>
       </x:c>
       <x:c r="O22" s="7" t="str">
-        <x:v>OutOfStock</x:v>
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="P22" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q22" s="7" t="str">
-        <x:v>0201-10pF-50V-10%</x:v>
+        <x:v>CC0402KRX7R0BB103</x:v>
       </x:c>
       <x:c r="R22" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C561710.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C527014.html</x:v>
       </x:c>
       <x:c r="S22" s="7" t="str">
-        <x:v>Package: 0201; Capacitance: 10pF; Temperature Coefficient: C0G; Tolerance: ±5%; Voltage Rating: 50V</x:v>
+        <x:v>Package: 0402; Capacitance: 10nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 100V</x:v>
       </x:c>
       <x:c r="T22" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C29,C32</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C52</x:v>
       </x:c>
       <x:c r="U22" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -8503,42 +8807,42 @@
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
       <x:c r="A23" s="7" t="str">
-        <x:v>C576517</x:v>
+        <x:v>C52923</x:v>
       </x:c>
       <x:c r="B23" s="7" t="str">
-        <x:v>GRM32EC72A106KE05L</x:v>
+        <x:v>CL05A105KA5NQNC</x:v>
       </x:c>
       <x:c r="C23" s="7" t="str">
-        <x:v>muRata</x:v>
+        <x:v>SAMSUNG</x:v>
       </x:c>
       <x:c r="D23" s="7" t="str">
-        <x:v>10uF ±10% 100V Ceramic Capacitor X7S 1210</x:v>
+        <x:v>1uF ±10% 25V Ceramic Capacitor X5R</x:v>
       </x:c>
       <x:c r="E23" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F23" s="7" t="str">
-        <x:v>GRM32EC72A106KE05L</x:v>
+        <x:v>CL05A105KA5NQNC</x:v>
       </x:c>
       <x:c r="G23" s="7" t="str">
-        <x:v>C1210</x:v>
+        <x:v>C0402</x:v>
       </x:c>
       <x:c r="H23" s="7" t="str">
-        <x:v>10uF</x:v>
+        <x:v>1uF</x:v>
       </x:c>
       <x:c r="I23" s="7" t="str">
-        <x:v>1210</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J23" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/a5661d5fbdf2b41a50853cb83d84d655.pdf?productCode=C576517</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20160218/1457707763339.pdf</x:v>
       </x:c>
       <x:c r="K23" s="7" t="str"/>
       <x:c r="L23" s="7" t="str"/>
       <x:c r="M23" s="7" t="str">
-        <x:v>../datasheets/C576517/GRM32EC72A106KE05L.pdf</x:v>
+        <x:v>../datasheets/C52923/CL05A105KA5NQNC.pdf</x:v>
       </x:c>
       <x:c r="N23" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C1210_L3.2-W2.5-H2.5.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0402_L1.0-W0.5-H0.5.wrl</x:v>
       </x:c>
       <x:c r="O23" s="7" t="str">
         <x:v>Active</x:v>
@@ -8547,22 +8851,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q23" s="7" t="str">
-        <x:v>C1210</x:v>
+        <x:v>0402-1uF-10V-10%</x:v>
       </x:c>
       <x:c r="R23" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C576517.html</x:v>
+        <x:v>https://item.szlcsc.com/53938.html</x:v>
       </x:c>
       <x:c r="S23" s="7" t="str">
-        <x:v>Package: 1210; Capacitance: 10uF; Temperature Coefficient: X7S; Tolerance: ±10%; Voltage Rating: 100V</x:v>
+        <x:v>Package: 0402; Capacitance: 1uF; Tolerance: ±10%; Voltage Rating: 25V; Temperature Coefficient: X5R</x:v>
       </x:c>
       <x:c r="T23" s="7" t="str">
-        <x:v>Designators: C2, C3, C5, C6, C7, C8, C17, C46, C47, C48, C81, C82, C83, C87, C88</x:v>
+        <x:v>Designators: Y43-C2,C4,C5,C7,C16</x:v>
       </x:c>
       <x:c r="U23" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V23" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>Y43</x:v>
       </x:c>
       <x:c r="W23" s="7" t="str">
         <x:v>Capacitors</x:v>
@@ -8579,66 +8883,66 @@
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
       <x:c r="A24" s="7" t="str">
-        <x:v>C577211</x:v>
+        <x:v>C561710</x:v>
       </x:c>
       <x:c r="B24" s="7" t="str">
-        <x:v>CC1206KKX7R0BB225</x:v>
+        <x:v>FN03N100J500PLG</x:v>
       </x:c>
       <x:c r="C24" s="7" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>PSA</x:v>
       </x:c>
       <x:c r="D24" s="7" t="str">
-        <x:v>2.2uF ±10% 100V Ceramic Capacitor X7R 1206</x:v>
+        <x:v>10pF ±5% 50V Ceramic Capacitor C0G 0201</x:v>
       </x:c>
       <x:c r="E24" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F24" s="7" t="str">
-        <x:v>CC1206KKX7R0BB225</x:v>
+        <x:v>FN03N100J500PLG</x:v>
       </x:c>
       <x:c r="G24" s="7" t="str">
-        <x:v>C1206</x:v>
+        <x:v>C_0201_0603Metric</x:v>
       </x:c>
       <x:c r="H24" s="7" t="str">
-        <x:v>2.2uF</x:v>
+        <x:v>10pF</x:v>
       </x:c>
       <x:c r="I24" s="7" t="str">
-        <x:v>1206</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J24" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/23ccee80ee542e7cf156a772bb589942.pdf?productCode=C577211</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/1497a6a2cea2f2b0acf5e045d2bc193c.pdf?productCode=C561710</x:v>
       </x:c>
       <x:c r="K24" s="7" t="str"/>
       <x:c r="L24" s="7" t="str"/>
       <x:c r="M24" s="7" t="str">
-        <x:v>../datasheets/C577211/CC1206KKX7R0BB225.pdf</x:v>
+        <x:v>../datasheets/C561710/FN03N100J500PLG.pdf</x:v>
       </x:c>
       <x:c r="N24" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C1206_L3.2-W1.6-H1.3.wrl</x:v>
+        <x:v>${KICAD10_3DMODEL_DIR}/Capacitor_SMD.3dshapes/C_0201_0603Metric.step</x:v>
       </x:c>
       <x:c r="O24" s="7" t="str">
-        <x:v>Active</x:v>
+        <x:v>OutOfStock</x:v>
       </x:c>
       <x:c r="P24" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q24" s="7" t="str">
-        <x:v>C1206</x:v>
+        <x:v>0201-10pF-50V-10%</x:v>
       </x:c>
       <x:c r="R24" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C577211.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C561710.html</x:v>
       </x:c>
       <x:c r="S24" s="7" t="str">
-        <x:v>Package: 1206; Capacitance: 2.2uF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 100V</x:v>
+        <x:v>Package: 0201; Capacitance: 10pF; Temperature Coefficient: C0G; Tolerance: ±5%; Voltage Rating: 50V</x:v>
       </x:c>
       <x:c r="T24" s="7" t="str">
-        <x:v>Designators: C12</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C29,C32</x:v>
       </x:c>
       <x:c r="U24" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V24" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>legacy_import</x:v>
       </x:c>
       <x:c r="W24" s="7" t="str">
         <x:v>Capacitors</x:v>
@@ -8655,42 +8959,42 @@
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
       <x:c r="A25" s="7" t="str">
-        <x:v>C596322</x:v>
+        <x:v>C561711</x:v>
       </x:c>
       <x:c r="B25" s="7" t="str">
-        <x:v>CC1206JKNPOZBN222</x:v>
+        <x:v>FN03N101J500PLG</x:v>
       </x:c>
       <x:c r="C25" s="7" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>PSA(信昌电陶)</x:v>
       </x:c>
       <x:c r="D25" s="7" t="str">
-        <x:v>2.2nF ±5% 630V Ceramic Capacitor NP0 1206</x:v>
+        <x:v>100pF 50V 5% 0201 ceramic capacitor</x:v>
       </x:c>
       <x:c r="E25" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F25" s="7" t="str">
-        <x:v>CC1206JKNPOZBN222</x:v>
+        <x:v>FN03N101J500PLG</x:v>
       </x:c>
       <x:c r="G25" s="7" t="str">
-        <x:v>C1206</x:v>
+        <x:v>C_0201_0603Metric</x:v>
       </x:c>
       <x:c r="H25" s="7" t="str">
-        <x:v>2.2nF</x:v>
+        <x:v>100pF</x:v>
       </x:c>
       <x:c r="I25" s="7" t="str">
-        <x:v>1206</x:v>
+        <x:v>0201</x:v>
       </x:c>
       <x:c r="J25" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/9a86cbae8c34c796174906a7ab23dad0.pdf?productCode=C596322</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20241107/25D13BC56D84FBEC5B349398FCEBBC16.pdf</x:v>
       </x:c>
       <x:c r="K25" s="7" t="str"/>
       <x:c r="L25" s="7" t="str"/>
       <x:c r="M25" s="7" t="str">
-        <x:v>../datasheets/C596322/CC1206JKNPOZBN222.pdf</x:v>
+        <x:v>../datasheets/C561711/FN03N101J500PLG.pdf</x:v>
       </x:c>
       <x:c r="N25" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C1206_L3.2-W1.6-H1.3.wrl</x:v>
+        <x:v>${KICAD10_3DMODEL_DIR}/Capacitor_SMD.3dshapes/C_0201_0603Metric.step</x:v>
       </x:c>
       <x:c r="O25" s="7" t="str">
         <x:v>Active</x:v>
@@ -8699,22 +9003,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q25" s="7" t="str">
-        <x:v>CC1206JKNPOZBN222</x:v>
+        <x:v>C0201</x:v>
       </x:c>
       <x:c r="R25" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C596322.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C561711.html</x:v>
       </x:c>
       <x:c r="S25" s="7" t="str">
-        <x:v>Package: 1206; Capacitance: 2.2nF; Temperature Coefficient: NP0; Tolerance: ±5%; Voltage Rating: 630V</x:v>
+        <x:v>Package: 0201; Capacitance: 100pF; Voltage: 50V; Tolerance: 5%</x:v>
       </x:c>
       <x:c r="T25" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C14,C18</x:v>
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designators C15/C16/C17/C20.</x:v>
       </x:c>
       <x:c r="U25" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V25" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809; legacy_import</x:v>
+        <x:v>EBOM_V1.10</x:v>
       </x:c>
       <x:c r="W25" s="7" t="str">
         <x:v>Capacitors</x:v>
@@ -8731,42 +9035,42 @@
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
       <x:c r="A26" s="7" t="str">
-        <x:v>C60137</x:v>
+        <x:v>C576517</x:v>
       </x:c>
       <x:c r="B26" s="7" t="str">
-        <x:v>CC0402JRNPO9BN470</x:v>
+        <x:v>GRM32EC72A106KE05L</x:v>
       </x:c>
       <x:c r="C26" s="7" t="str">
-        <x:v>YAGEO</x:v>
+        <x:v>muRata</x:v>
       </x:c>
       <x:c r="D26" s="7" t="str">
-        <x:v>47pF ±5% 50V Ceramic Capacitor NP0 0402</x:v>
+        <x:v>10uF ±10% 100V Ceramic Capacitor X7S 1210</x:v>
       </x:c>
       <x:c r="E26" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F26" s="7" t="str">
-        <x:v>CC0402JRNPO9BN470</x:v>
+        <x:v>GRM32EC72A106KE05L</x:v>
       </x:c>
       <x:c r="G26" s="7" t="str">
-        <x:v>C0402</x:v>
+        <x:v>C1210</x:v>
       </x:c>
       <x:c r="H26" s="7" t="str">
-        <x:v>47pF</x:v>
+        <x:v>10uF</x:v>
       </x:c>
       <x:c r="I26" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>1210</x:v>
       </x:c>
       <x:c r="J26" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/4eca2bb4b507f1633db47e922d632b95.pdf?productCode=C60137</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/a5661d5fbdf2b41a50853cb83d84d655.pdf?productCode=C576517</x:v>
       </x:c>
       <x:c r="K26" s="7" t="str"/>
       <x:c r="L26" s="7" t="str"/>
       <x:c r="M26" s="7" t="str">
-        <x:v>../datasheets/C60137/CC0402JRNPO9BN470.pdf</x:v>
+        <x:v>../datasheets/C576517/GRM32EC72A106KE05L.pdf</x:v>
       </x:c>
       <x:c r="N26" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0402_L1.0-W0.5-H0.5.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C1210_L3.2-W2.5-H2.5.wrl</x:v>
       </x:c>
       <x:c r="O26" s="7" t="str">
         <x:v>Active</x:v>
@@ -8775,16 +9079,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q26" s="7" t="str">
-        <x:v>C0402</x:v>
+        <x:v>C1210</x:v>
       </x:c>
       <x:c r="R26" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C60137.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C576517.html</x:v>
       </x:c>
       <x:c r="S26" s="7" t="str">
-        <x:v>Package: 0402; Capacitance: 47pF; Temperature Coefficient: NP0; Tolerance: ±5%; Voltage Rating: 50V</x:v>
+        <x:v>Package: 1210; Capacitance: 10uF; Temperature Coefficient: X7S; Tolerance: ±10%; Voltage Rating: 100V</x:v>
       </x:c>
       <x:c r="T26" s="7" t="str">
-        <x:v>Designators: C35</x:v>
+        <x:v>Designators: C2, C3, C5, C6, C7, C8, C17, C46, C47, C48, C81, C82, C83, C87, C88</x:v>
       </x:c>
       <x:c r="U26" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -8807,42 +9111,42 @@
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
       <x:c r="A27" s="7" t="str">
-        <x:v>C668346</x:v>
+        <x:v>C577211</x:v>
       </x:c>
       <x:c r="B27" s="7" t="str">
-        <x:v>GRM033Z71C104KE14D</x:v>
+        <x:v>CC1206KKX7R0BB225</x:v>
       </x:c>
       <x:c r="C27" s="7" t="str">
-        <x:v>muRata</x:v>
+        <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D27" s="7" t="str">
-        <x:v>100nF ±10% 16V Ceramic Capacitor X7R 0201</x:v>
+        <x:v>2.2uF ±10% 100V Ceramic Capacitor X7R 1206</x:v>
       </x:c>
       <x:c r="E27" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F27" s="7" t="str">
-        <x:v>GRM033Z71C104KE14D</x:v>
+        <x:v>CC1206KKX7R0BB225</x:v>
       </x:c>
       <x:c r="G27" s="7" t="str">
-        <x:v>C0201</x:v>
+        <x:v>C1206</x:v>
       </x:c>
       <x:c r="H27" s="7" t="str">
-        <x:v>100nF</x:v>
+        <x:v>2.2uF</x:v>
       </x:c>
       <x:c r="I27" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>1206</x:v>
       </x:c>
       <x:c r="J27" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/0fb4604782167a586c3dd1f22396ac96.pdf?productCode=C668346</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/23ccee80ee542e7cf156a772bb589942.pdf?productCode=C577211</x:v>
       </x:c>
       <x:c r="K27" s="7" t="str"/>
       <x:c r="L27" s="7" t="str"/>
       <x:c r="M27" s="7" t="str">
-        <x:v>../datasheets/C668346/GRM033Z71C104KE14D.pdf</x:v>
+        <x:v>../datasheets/C577211/CC1206KKX7R0BB225.pdf</x:v>
       </x:c>
       <x:c r="N27" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0201_L0.6-W0.3-H0.3.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C1206_L3.2-W1.6-H1.3.wrl</x:v>
       </x:c>
       <x:c r="O27" s="7" t="str">
         <x:v>Active</x:v>
@@ -8851,22 +9155,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q27" s="7" t="str">
-        <x:v>0201-100nF-16V-10%</x:v>
+        <x:v>C1206</x:v>
       </x:c>
       <x:c r="R27" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C668346.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C577211.html</x:v>
       </x:c>
       <x:c r="S27" s="7" t="str">
-        <x:v>Package: 0201; Capacitance: 100nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 16V</x:v>
+        <x:v>Package: 1206; Capacitance: 2.2uF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 100V</x:v>
       </x:c>
       <x:c r="T27" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls, BOM_PASTER_8984112A_Y189.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C1,C6,C12,C13,C21,C26,C27,C30,C31,C33,C34,C38,C46,C47,C48,C49,C50,C54,C55,C58,C59,C60; BOM_PASTER_8984112A_Y185.xls: C1,C2,C3,C4,C6,C7,C9,C12,C14,C21,C24; BOM_PASTER_8984112A_Y189.xls: C1</x:v>
+        <x:v>Designators: C12</x:v>
       </x:c>
       <x:c r="U27" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V27" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
       <x:c r="W27" s="7" t="str">
         <x:v>Capacitors</x:v>
@@ -8883,66 +9187,66 @@
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
       <x:c r="A28" s="7" t="str">
-        <x:v>C730413</x:v>
+        <x:v>C596322</x:v>
       </x:c>
       <x:c r="B28" s="7" t="str">
-        <x:v>CL03C101JB3NNNC</x:v>
+        <x:v>CC1206JKNPOZBN222</x:v>
       </x:c>
       <x:c r="C28" s="7" t="str">
-        <x:v>Samsung Electro-Mechanics</x:v>
+        <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D28" s="7" t="str">
-        <x:v>100pF ±5% 50V Ceramic Capacitor C0G 0201</x:v>
+        <x:v>2.2nF ±5% 630V Ceramic Capacitor NP0 1206</x:v>
       </x:c>
       <x:c r="E28" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F28" s="7" t="str">
-        <x:v>CL03C101JB3NNNC</x:v>
+        <x:v>CC1206JKNPOZBN222</x:v>
       </x:c>
       <x:c r="G28" s="7" t="str">
-        <x:v>C0201</x:v>
+        <x:v>C1206</x:v>
       </x:c>
       <x:c r="H28" s="7" t="str">
-        <x:v>100pF</x:v>
+        <x:v>2.2nF</x:v>
       </x:c>
       <x:c r="I28" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>1206</x:v>
       </x:c>
       <x:c r="J28" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/02336ea48ea44ca18c72517dd3cb7b47.pdf?productCode=C730413</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/9a86cbae8c34c796174906a7ab23dad0.pdf?productCode=C596322</x:v>
       </x:c>
       <x:c r="K28" s="7" t="str"/>
       <x:c r="L28" s="7" t="str"/>
       <x:c r="M28" s="7" t="str">
-        <x:v>../datasheets/C730413/CL03C101JB3NNNC.pdf</x:v>
+        <x:v>../datasheets/C596322/CC1206JKNPOZBN222.pdf</x:v>
       </x:c>
       <x:c r="N28" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0201_L0.6-W0.3-H0.3.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C1206_L3.2-W1.6-H1.3.wrl</x:v>
       </x:c>
       <x:c r="O28" s="7" t="str">
-        <x:v>OutOfStock</x:v>
+        <x:v>Active</x:v>
       </x:c>
       <x:c r="P28" s="7" t="str">
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q28" s="7" t="str">
-        <x:v>0201-100pF-50V-5%</x:v>
+        <x:v>CC1206JKNPOZBN222</x:v>
       </x:c>
       <x:c r="R28" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C730413.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C596322.html</x:v>
       </x:c>
       <x:c r="S28" s="7" t="str">
-        <x:v>Package: 0201; Capacitance: 100pF; Temperature Coefficient: C0G; Tolerance: ±5%; Voltage Rating: 50V</x:v>
+        <x:v>Package: 1206; Capacitance: 2.2nF; Temperature Coefficient: NP0; Tolerance: ±5%; Voltage Rating: 630V</x:v>
       </x:c>
       <x:c r="T28" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C3,C4,C5,C9,C10,C11,C24,C35,C36,C37,C39,C40,C42,C43,C44,C45; BOM_PASTER_8984112A_Y185.xls: C18,C19,C20,C22</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C14,C18</x:v>
       </x:c>
       <x:c r="U28" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V28" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809; legacy_import</x:v>
       </x:c>
       <x:c r="W28" s="7" t="str">
         <x:v>Capacitors</x:v>
@@ -8959,42 +9263,42 @@
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
       <x:c r="A29" s="7" t="str">
-        <x:v>C730422</x:v>
+        <x:v>C60137</x:v>
       </x:c>
       <x:c r="B29" s="7" t="str">
-        <x:v>CL03Y104KO3NNNC</x:v>
+        <x:v>CC0402JRNPO9BN470</x:v>
       </x:c>
       <x:c r="C29" s="7" t="str">
-        <x:v>SAMSUNG</x:v>
+        <x:v>YAGEO</x:v>
       </x:c>
       <x:c r="D29" s="7" t="str">
-        <x:v>100nF ±10% 16V Ceramic Capacitor X7R</x:v>
+        <x:v>47pF ±5% 50V Ceramic Capacitor NP0 0402</x:v>
       </x:c>
       <x:c r="E29" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F29" s="7" t="str">
-        <x:v>CL03Y104KO3NNNC</x:v>
+        <x:v>CC0402JRNPO9BN470</x:v>
       </x:c>
       <x:c r="G29" s="7" t="str">
-        <x:v>C0201</x:v>
+        <x:v>C0402</x:v>
       </x:c>
       <x:c r="H29" s="7" t="str">
-        <x:v>100nF</x:v>
+        <x:v>47pF</x:v>
       </x:c>
       <x:c r="I29" s="7" t="str">
-        <x:v>0201</x:v>
+        <x:v>0402</x:v>
       </x:c>
       <x:c r="J29" s="7" t="str">
-        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20160218/1457707763339.pdf</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/4eca2bb4b507f1633db47e922d632b95.pdf?productCode=C60137</x:v>
       </x:c>
       <x:c r="K29" s="7" t="str"/>
       <x:c r="L29" s="7" t="str"/>
       <x:c r="M29" s="7" t="str">
-        <x:v>../datasheets/C730422/CL03Y104KO3NNNC.pdf</x:v>
+        <x:v>../datasheets/C60137/CC0402JRNPO9BN470.pdf</x:v>
       </x:c>
       <x:c r="N29" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0201_L0.6-W0.3-H0.3.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0402_L1.0-W0.5-H0.5.wrl</x:v>
       </x:c>
       <x:c r="O29" s="7" t="str">
         <x:v>Active</x:v>
@@ -9003,22 +9307,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q29" s="7" t="str">
-        <x:v>0201-100nF-16V-10%</x:v>
+        <x:v>C0402</x:v>
       </x:c>
       <x:c r="R29" s="7" t="str">
-        <x:v>https://item.szlcsc.com/778821.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C60137.html</x:v>
       </x:c>
       <x:c r="S29" s="7" t="str">
-        <x:v>Package: 0201; Capacitance: 100nF; Tolerance: ±10%; Voltage Rating: 16V; Temperature Coefficient: X7R</x:v>
+        <x:v>Package: 0402; Capacitance: 47pF; Temperature Coefficient: NP0; Tolerance: ±5%; Voltage Rating: 50V</x:v>
       </x:c>
       <x:c r="T29" s="7" t="str">
-        <x:v>Designators: Y43-C17; Z300BL-C17</x:v>
+        <x:v>Designators: C35</x:v>
       </x:c>
       <x:c r="U29" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V29" s="7" t="str">
-        <x:v>Y43; Z300BL</x:v>
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
       </x:c>
       <x:c r="W29" s="7" t="str">
         <x:v>Capacitors</x:v>
@@ -9035,42 +9339,42 @@
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
       <x:c r="A30" s="7" t="str">
-        <x:v>C76941</x:v>
+        <x:v>C668346</x:v>
       </x:c>
       <x:c r="B30" s="7" t="str">
-        <x:v>GRM033R71A103KA01D</x:v>
+        <x:v>GRM033Z71C104KE14D</x:v>
       </x:c>
       <x:c r="C30" s="7" t="str">
         <x:v>muRata</x:v>
       </x:c>
       <x:c r="D30" s="7" t="str">
-        <x:v>10nF ±10% 10V Ceramic Capacitor X7R 0201</x:v>
+        <x:v>100nF ±10% 16V Ceramic Capacitor X7R 0201</x:v>
       </x:c>
       <x:c r="E30" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F30" s="7" t="str">
-        <x:v>GRM033R71A103KA01D</x:v>
+        <x:v>GRM033Z71C104KE14D</x:v>
       </x:c>
       <x:c r="G30" s="7" t="str">
-        <x:v>C_0201_0603Metric</x:v>
+        <x:v>C0201</x:v>
       </x:c>
       <x:c r="H30" s="7" t="str">
-        <x:v>10nF</x:v>
+        <x:v>100nF</x:v>
       </x:c>
       <x:c r="I30" s="7" t="str">
         <x:v>0201</x:v>
       </x:c>
       <x:c r="J30" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/58a7d404c3534585b4a0e91caba788f7.pdf?productCode=C76941</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/0fb4604782167a586c3dd1f22396ac96.pdf?productCode=C668346</x:v>
       </x:c>
       <x:c r="K30" s="7" t="str"/>
       <x:c r="L30" s="7" t="str"/>
       <x:c r="M30" s="7" t="str">
-        <x:v>../datasheets/C76941/GRM033R71A103KA01D.pdf</x:v>
+        <x:v>../datasheets/C668346/GRM033Z71C104KE14D.pdf</x:v>
       </x:c>
       <x:c r="N30" s="7" t="str">
-        <x:v>${KICAD10_3DMODEL_DIR}/Capacitor_SMD.3dshapes/C_0201_0603Metric.step</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0201_L0.6-W0.3-H0.3.wrl</x:v>
       </x:c>
       <x:c r="O30" s="7" t="str">
         <x:v>Active</x:v>
@@ -9079,16 +9383,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q30" s="7" t="str">
-        <x:v>0201-10nF-10V-10%</x:v>
+        <x:v>0201-100nF-16V-10%</x:v>
       </x:c>
       <x:c r="R30" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C76941.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C668346.html</x:v>
       </x:c>
       <x:c r="S30" s="7" t="str">
-        <x:v>Package: 0201; Capacitance: 10nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 10V</x:v>
+        <x:v>Package: 0201; Capacitance: 100nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 16V</x:v>
       </x:c>
       <x:c r="T30" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y185.xls: C10</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls, BOM_PASTER_8984112A_Y189.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C1,C6,C12,C13,C21,C26,C27,C30,C31,C33,C34,C38,C46,C47,C48,C49,C50,C54,C55,C58,C59,C60; BOM_PASTER_8984112A_Y185.xls: C1,C2,C3,C4,C6,C7,C9,C12,C14,C21,C24; BOM_PASTER_8984112A_Y189.xls: C1</x:v>
       </x:c>
       <x:c r="U30" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -9111,42 +9415,42 @@
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
       <x:c r="A31" s="7" t="str">
-        <x:v>C77020</x:v>
+        <x:v>C694230</x:v>
       </x:c>
       <x:c r="B31" s="7" t="str">
-        <x:v>GRM155R71H104KE14D</x:v>
+        <x:v>CGA4J1X7S1E106KT0Y0N</x:v>
       </x:c>
       <x:c r="C31" s="7" t="str">
-        <x:v>muRata</x:v>
+        <x:v>TDK</x:v>
       </x:c>
       <x:c r="D31" s="7" t="str">
-        <x:v>100nF ±10% 50V Ceramic Capacitor X7R 0402</x:v>
+        <x:v>10uF 25V X7S 0805 ceramic capacitor</x:v>
       </x:c>
       <x:c r="E31" s="7" t="str">
         <x:v>Capacitors/Ceramic Capacitors</x:v>
       </x:c>
       <x:c r="F31" s="7" t="str">
-        <x:v>GRM155R71H104KE14D</x:v>
+        <x:v>CGA4J1X7S1E106KT0Y0N</x:v>
       </x:c>
       <x:c r="G31" s="7" t="str">
-        <x:v>C_0402_1005Metric</x:v>
+        <x:v>C_0805_2012Metric</x:v>
       </x:c>
       <x:c r="H31" s="7" t="str">
-        <x:v>100nF</x:v>
+        <x:v>10uF</x:v>
       </x:c>
       <x:c r="I31" s="7" t="str">
-        <x:v>0402</x:v>
+        <x:v>0805</x:v>
       </x:c>
       <x:c r="J31" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/64ac52ef9cc4e1905eba7e2ece85e662.pdf?productCode=C77020</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20200407/C342975_AB13C551805E4B495BBDB585D2C58CA0.pdf</x:v>
       </x:c>
       <x:c r="K31" s="7" t="str"/>
       <x:c r="L31" s="7" t="str"/>
       <x:c r="M31" s="7" t="str">
-        <x:v>../datasheets/C77020/GRM155R71H104KE14D.pdf</x:v>
+        <x:v>../datasheets/C694230/CGA4J1X7S1E106KT0Y0N.pdf</x:v>
       </x:c>
       <x:c r="N31" s="7" t="str">
-        <x:v>${KICAD10_3DMODEL_DIR}/Capacitor_SMD.3dshapes/C_0402_1005Metric.step</x:v>
+        <x:v>${KICAD10_3DMODEL_DIR}/Capacitor_SMD.3dshapes/C_0805_2012Metric.step</x:v>
       </x:c>
       <x:c r="O31" s="7" t="str">
         <x:v>Active</x:v>
@@ -9155,22 +9459,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q31" s="7" t="str">
-        <x:v>C0402</x:v>
+        <x:v>C0805</x:v>
       </x:c>
       <x:c r="R31" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C77020.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C694230.html</x:v>
       </x:c>
       <x:c r="S31" s="7" t="str">
-        <x:v>Package: 0402; Capacitance: 100nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 50V</x:v>
+        <x:v>Package: 0805; Capacitance: 10uF; Voltage: 25V; Tolerance: 10%; Temperature Coefficient: X7S</x:v>
       </x:c>
       <x:c r="T31" s="7" t="str">
-        <x:v>Designators: C10, C18, C19, C20, C23, C24, C25, C26, C30, C32, C34, C36, C38, C39, C40, C41, C42, C43, C44, C50, C51, C72, C77, C78</x:v>
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designator C18.</x:v>
       </x:c>
       <x:c r="U31" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V31" s="7" t="str">
-        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+        <x:v>EBOM_V1.10</x:v>
       </x:c>
       <x:c r="W31" s="7" t="str">
         <x:v>Capacitors</x:v>
@@ -9185,16 +9489,320 @@
         <x:v>CONVERTED</x:v>
       </x:c>
     </x:row>
+    <x:row r="32" ht="24" customHeight="1">
+      <x:c r="A32" s="7" t="str">
+        <x:v>C730413</x:v>
+      </x:c>
+      <x:c r="B32" s="7" t="str">
+        <x:v>CL03C101JB3NNNC</x:v>
+      </x:c>
+      <x:c r="C32" s="7" t="str">
+        <x:v>Samsung Electro-Mechanics</x:v>
+      </x:c>
+      <x:c r="D32" s="7" t="str">
+        <x:v>100pF ±5% 50V Ceramic Capacitor C0G 0201</x:v>
+      </x:c>
+      <x:c r="E32" s="7" t="str">
+        <x:v>Capacitors/Ceramic Capacitors</x:v>
+      </x:c>
+      <x:c r="F32" s="7" t="str">
+        <x:v>CL03C101JB3NNNC</x:v>
+      </x:c>
+      <x:c r="G32" s="7" t="str">
+        <x:v>C0201</x:v>
+      </x:c>
+      <x:c r="H32" s="7" t="str">
+        <x:v>100pF</x:v>
+      </x:c>
+      <x:c r="I32" s="7" t="str">
+        <x:v>0201</x:v>
+      </x:c>
+      <x:c r="J32" s="7" t="str">
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/02336ea48ea44ca18c72517dd3cb7b47.pdf?productCode=C730413</x:v>
+      </x:c>
+      <x:c r="K32" s="7" t="str"/>
+      <x:c r="L32" s="7" t="str"/>
+      <x:c r="M32" s="7" t="str">
+        <x:v>../datasheets/C730413/CL03C101JB3NNNC.pdf</x:v>
+      </x:c>
+      <x:c r="N32" s="7" t="str">
+        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0201_L0.6-W0.3-H0.3.wrl</x:v>
+      </x:c>
+      <x:c r="O32" s="7" t="str">
+        <x:v>OutOfStock</x:v>
+      </x:c>
+      <x:c r="P32" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q32" s="7" t="str">
+        <x:v>0201-100pF-50V-5%</x:v>
+      </x:c>
+      <x:c r="R32" s="7" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C730413.html</x:v>
+      </x:c>
+      <x:c r="S32" s="7" t="str">
+        <x:v>Package: 0201; Capacitance: 100pF; Temperature Coefficient: C0G; Tolerance: ±5%; Voltage Rating: 50V</x:v>
+      </x:c>
+      <x:c r="T32" s="7" t="str">
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls, BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y182.xls: C3,C4,C5,C9,C10,C11,C24,C35,C36,C37,C39,C40,C42,C43,C44,C45; BOM_PASTER_8984112A_Y185.xls: C18,C19,C20,C22</x:v>
+      </x:c>
+      <x:c r="U32" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V32" s="7" t="str">
+        <x:v>legacy_import</x:v>
+      </x:c>
+      <x:c r="W32" s="7" t="str">
+        <x:v>Capacitors</x:v>
+      </x:c>
+      <x:c r="X32" s="7" t="str">
+        <x:v>Capacitors.kicad_sym</x:v>
+      </x:c>
+      <x:c r="Y32" s="7" t="str">
+        <x:v>Capacitors.pretty</x:v>
+      </x:c>
+      <x:c r="Z32" s="7" t="str">
+        <x:v>CONVERTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="24" customHeight="1">
+      <x:c r="A33" s="7" t="str">
+        <x:v>C730422</x:v>
+      </x:c>
+      <x:c r="B33" s="7" t="str">
+        <x:v>CL03Y104KO3NNNC</x:v>
+      </x:c>
+      <x:c r="C33" s="7" t="str">
+        <x:v>SAMSUNG</x:v>
+      </x:c>
+      <x:c r="D33" s="7" t="str">
+        <x:v>100nF ±10% 16V Ceramic Capacitor X7R</x:v>
+      </x:c>
+      <x:c r="E33" s="7" t="str">
+        <x:v>Capacitors/Ceramic Capacitors</x:v>
+      </x:c>
+      <x:c r="F33" s="7" t="str">
+        <x:v>CL03Y104KO3NNNC</x:v>
+      </x:c>
+      <x:c r="G33" s="7" t="str">
+        <x:v>C0201</x:v>
+      </x:c>
+      <x:c r="H33" s="7" t="str">
+        <x:v>100nF</x:v>
+      </x:c>
+      <x:c r="I33" s="7" t="str">
+        <x:v>0201</x:v>
+      </x:c>
+      <x:c r="J33" s="7" t="str">
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20160218/1457707763339.pdf</x:v>
+      </x:c>
+      <x:c r="K33" s="7" t="str"/>
+      <x:c r="L33" s="7" t="str"/>
+      <x:c r="M33" s="7" t="str">
+        <x:v>../datasheets/C730422/CL03Y104KO3NNNC.pdf</x:v>
+      </x:c>
+      <x:c r="N33" s="7" t="str">
+        <x:v>${LCSC_LIB_ROOT}/Capacitors/Capacitors.3dshapes/C0201_L0.6-W0.3-H0.3.wrl</x:v>
+      </x:c>
+      <x:c r="O33" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P33" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q33" s="7" t="str">
+        <x:v>0201-100nF-16V-10%</x:v>
+      </x:c>
+      <x:c r="R33" s="7" t="str">
+        <x:v>https://item.szlcsc.com/778821.html</x:v>
+      </x:c>
+      <x:c r="S33" s="7" t="str">
+        <x:v>Package: 0201; Capacitance: 100nF; Tolerance: ±10%; Voltage Rating: 16V; Temperature Coefficient: X7R</x:v>
+      </x:c>
+      <x:c r="T33" s="7" t="str">
+        <x:v>Designators: Y43-C17; Z300BL-C17</x:v>
+      </x:c>
+      <x:c r="U33" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V33" s="7" t="str">
+        <x:v>Y43; Z300BL</x:v>
+      </x:c>
+      <x:c r="W33" s="7" t="str">
+        <x:v>Capacitors</x:v>
+      </x:c>
+      <x:c r="X33" s="7" t="str">
+        <x:v>Capacitors.kicad_sym</x:v>
+      </x:c>
+      <x:c r="Y33" s="7" t="str">
+        <x:v>Capacitors.pretty</x:v>
+      </x:c>
+      <x:c r="Z33" s="7" t="str">
+        <x:v>CONVERTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="24" customHeight="1">
+      <x:c r="A34" s="7" t="str">
+        <x:v>C76941</x:v>
+      </x:c>
+      <x:c r="B34" s="7" t="str">
+        <x:v>GRM033R71A103KA01D</x:v>
+      </x:c>
+      <x:c r="C34" s="7" t="str">
+        <x:v>muRata</x:v>
+      </x:c>
+      <x:c r="D34" s="7" t="str">
+        <x:v>10nF ±10% 10V Ceramic Capacitor X7R 0201</x:v>
+      </x:c>
+      <x:c r="E34" s="7" t="str">
+        <x:v>Capacitors/Ceramic Capacitors</x:v>
+      </x:c>
+      <x:c r="F34" s="7" t="str">
+        <x:v>GRM033R71A103KA01D</x:v>
+      </x:c>
+      <x:c r="G34" s="7" t="str">
+        <x:v>C_0201_0603Metric</x:v>
+      </x:c>
+      <x:c r="H34" s="7" t="str">
+        <x:v>10nF</x:v>
+      </x:c>
+      <x:c r="I34" s="7" t="str">
+        <x:v>0201</x:v>
+      </x:c>
+      <x:c r="J34" s="7" t="str">
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/58a7d404c3534585b4a0e91caba788f7.pdf?productCode=C76941</x:v>
+      </x:c>
+      <x:c r="K34" s="7" t="str"/>
+      <x:c r="L34" s="7" t="str"/>
+      <x:c r="M34" s="7" t="str">
+        <x:v>../datasheets/C76941/GRM033R71A103KA01D.pdf</x:v>
+      </x:c>
+      <x:c r="N34" s="7" t="str">
+        <x:v>${KICAD10_3DMODEL_DIR}/Capacitor_SMD.3dshapes/C_0201_0603Metric.step</x:v>
+      </x:c>
+      <x:c r="O34" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P34" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q34" s="7" t="str">
+        <x:v>0201-10nF-10V-10%</x:v>
+      </x:c>
+      <x:c r="R34" s="7" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C76941.html</x:v>
+      </x:c>
+      <x:c r="S34" s="7" t="str">
+        <x:v>Package: 0201; Capacitance: 10nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 10V</x:v>
+      </x:c>
+      <x:c r="T34" s="7" t="str">
+        <x:v>Sources: BOM_PASTER_8984112A_Y185.xls; Designators: BOM_PASTER_8984112A_Y185.xls: C10</x:v>
+      </x:c>
+      <x:c r="U34" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V34" s="7" t="str">
+        <x:v>legacy_import</x:v>
+      </x:c>
+      <x:c r="W34" s="7" t="str">
+        <x:v>Capacitors</x:v>
+      </x:c>
+      <x:c r="X34" s="7" t="str">
+        <x:v>Capacitors.kicad_sym</x:v>
+      </x:c>
+      <x:c r="Y34" s="7" t="str">
+        <x:v>Capacitors.pretty</x:v>
+      </x:c>
+      <x:c r="Z34" s="7" t="str">
+        <x:v>CONVERTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="24" customHeight="1">
+      <x:c r="A35" s="7" t="str">
+        <x:v>C77020</x:v>
+      </x:c>
+      <x:c r="B35" s="7" t="str">
+        <x:v>GRM155R71H104KE14D</x:v>
+      </x:c>
+      <x:c r="C35" s="7" t="str">
+        <x:v>muRata</x:v>
+      </x:c>
+      <x:c r="D35" s="7" t="str">
+        <x:v>100nF ±10% 50V Ceramic Capacitor X7R 0402</x:v>
+      </x:c>
+      <x:c r="E35" s="7" t="str">
+        <x:v>Capacitors/Ceramic Capacitors</x:v>
+      </x:c>
+      <x:c r="F35" s="7" t="str">
+        <x:v>GRM155R71H104KE14D</x:v>
+      </x:c>
+      <x:c r="G35" s="7" t="str">
+        <x:v>C_0402_1005Metric</x:v>
+      </x:c>
+      <x:c r="H35" s="7" t="str">
+        <x:v>100nF</x:v>
+      </x:c>
+      <x:c r="I35" s="7" t="str">
+        <x:v>0402</x:v>
+      </x:c>
+      <x:c r="J35" s="7" t="str">
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/64ac52ef9cc4e1905eba7e2ece85e662.pdf?productCode=C77020</x:v>
+      </x:c>
+      <x:c r="K35" s="7" t="str"/>
+      <x:c r="L35" s="7" t="str"/>
+      <x:c r="M35" s="7" t="str">
+        <x:v>../datasheets/C77020/GRM155R71H104KE14D.pdf</x:v>
+      </x:c>
+      <x:c r="N35" s="7" t="str">
+        <x:v>${KICAD10_3DMODEL_DIR}/Capacitor_SMD.3dshapes/C_0402_1005Metric.step</x:v>
+      </x:c>
+      <x:c r="O35" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P35" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q35" s="7" t="str">
+        <x:v>C0402</x:v>
+      </x:c>
+      <x:c r="R35" s="7" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C77020.html</x:v>
+      </x:c>
+      <x:c r="S35" s="7" t="str">
+        <x:v>Package: 0402; Capacitance: 100nF; Temperature Coefficient: X7R; Tolerance: ±10%; Voltage Rating: 50V</x:v>
+      </x:c>
+      <x:c r="T35" s="7" t="str">
+        <x:v>Designators: C10, C18, C19, C20, C23, C24, C25, C26, C30, C32, C34, C36, C38, C39, C40, C41, C42, C43, C44, C50, C51, C72, C77, C78</x:v>
+      </x:c>
+      <x:c r="U35" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V35" s="7" t="str">
+        <x:v>X200T_ECU_B1_V1.0_20240809</x:v>
+      </x:c>
+      <x:c r="W35" s="7" t="str">
+        <x:v>Capacitors</x:v>
+      </x:c>
+      <x:c r="X35" s="7" t="str">
+        <x:v>Capacitors.kicad_sym</x:v>
+      </x:c>
+      <x:c r="Y35" s="7" t="str">
+        <x:v>Capacitors.pretty</x:v>
+      </x:c>
+      <x:c r="Z35" s="7" t="str">
+        <x:v>CONVERTED</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="U5:U31">
+  <x:conditionalFormatting sqref="U5:U35">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="CLASSIFIED_PARTIAL"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="Z5:Z31">
+  <x:conditionalFormatting sqref="Z5:Z35">
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="PENDING_CONVERSION"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd7395ec38364d48"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18bb27fbf1f244fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9934,7 +10542,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ede8c95d66a4644"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R089c72143f144c38"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9978,7 +10586,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="str">
-        <x:v>类别：Circuit Protection；记录数：1；来源：library_index.csv</x:v>
+        <x:v>类别：Circuit Protection；记录数：2；来源：library_index.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -10063,42 +10671,42 @@
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="7" t="str">
-        <x:v>C54582078</x:v>
+        <x:v>C123805</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>SLESD11LE5.0C</x:v>
+        <x:v>SMF16CA</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Slkor(萨科微)</x:v>
+        <x:v>MDD(辰达半导体)</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>0.3pF 5V bidirectional ESD protection diode, DFN0603-2L</x:v>
+        <x:v>16V 200W bidirectional TVS diode SOD-123FL</x:v>
       </x:c>
       <x:c r="E5" s="7" t="str">
-        <x:v>Circuit Protection/ESD Protection</x:v>
+        <x:v>Circuit Protection/TVS Diodes</x:v>
       </x:c>
       <x:c r="F5" s="7" t="str">
-        <x:v>SLESD11LE5.0C</x:v>
+        <x:v>SMF16CA</x:v>
       </x:c>
       <x:c r="G5" s="7" t="str">
-        <x:v>D_0201_0603Metric</x:v>
+        <x:v>D_SOD-123F</x:v>
       </x:c>
       <x:c r="H5" s="7" t="str">
-        <x:v>SLESD11LE5.0C</x:v>
+        <x:v>SMF16CA</x:v>
       </x:c>
       <x:c r="I5" s="7" t="str">
-        <x:v>DFN0603-2L</x:v>
+        <x:v>SOD-123FL</x:v>
       </x:c>
       <x:c r="J5" s="7" t="str">
-        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20260407/8CFBFE2B8741D426B78BD31A162E1949.pdf</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20250911/A9E208B97C1B87827444A0C468124C54.pdf</x:v>
       </x:c>
       <x:c r="K5" s="7" t="str"/>
       <x:c r="L5" s="7" t="str"/>
       <x:c r="M5" s="7" t="str">
-        <x:v>../datasheets/C54582078/SLESD11LE5.0C.pdf</x:v>
+        <x:v>../datasheets/C123805/SMF16CA.pdf</x:v>
       </x:c>
       <x:c r="N5" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Circuit Protection/Circuit Protection.3dshapes/DFN0603-2L-BI-1.wrl</x:v>
+        <x:v>${KICAD10_3DMODEL_DIR}/Diode_SMD.3dshapes/D_SOD-123F.step</x:v>
       </x:c>
       <x:c r="O5" s="7" t="str">
         <x:v>Active</x:v>
@@ -10107,22 +10715,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q5" s="7" t="str">
-        <x:v>DFN0603-2L</x:v>
+        <x:v>SOD-123FL</x:v>
       </x:c>
       <x:c r="R5" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C54582078.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C123805.html</x:v>
       </x:c>
       <x:c r="S5" s="7" t="str">
-        <x:v>Package: DFN0603-2L; Reverse Stand-Off Voltage: 5.0V; Capacitance: 0.3pF; Peak Pulse Current: 5.5A; ESD: ±30kV</x:v>
+        <x:v>Package: SOD-123FL; Reverse Stand-Off Voltage: 16V; Peak Pulse Power: 200W; Polarity: Bidirectional</x:v>
       </x:c>
       <x:c r="T5" s="7" t="str">
-        <x:v>Requested ESD diode; replaces legacy placeholder C9900301658.</x:v>
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designator D3.</x:v>
       </x:c>
       <x:c r="U5" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V5" s="7" t="str">
-        <x:v>LocalParts</x:v>
+        <x:v>EBOM_V1.10</x:v>
       </x:c>
       <x:c r="W5" s="7" t="str">
         <x:v>Circuit Protection</x:v>
@@ -10137,16 +10745,92 @@
         <x:v>CONVERTED</x:v>
       </x:c>
     </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="7" t="str">
+        <x:v>C54582078</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="str">
+        <x:v>SLESD11LE5.0C</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="str">
+        <x:v>Slkor(萨科微)</x:v>
+      </x:c>
+      <x:c r="D6" s="7" t="str">
+        <x:v>0.3pF 5V bidirectional ESD protection diode, DFN0603-2L</x:v>
+      </x:c>
+      <x:c r="E6" s="7" t="str">
+        <x:v>Circuit Protection/ESD Protection</x:v>
+      </x:c>
+      <x:c r="F6" s="7" t="str">
+        <x:v>SLESD11LE5.0C</x:v>
+      </x:c>
+      <x:c r="G6" s="7" t="str">
+        <x:v>D_0201_0603Metric</x:v>
+      </x:c>
+      <x:c r="H6" s="7" t="str">
+        <x:v>SLESD11LE5.0C</x:v>
+      </x:c>
+      <x:c r="I6" s="7" t="str">
+        <x:v>DFN0603-2L</x:v>
+      </x:c>
+      <x:c r="J6" s="7" t="str">
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20260407/8CFBFE2B8741D426B78BD31A162E1949.pdf</x:v>
+      </x:c>
+      <x:c r="K6" s="7" t="str"/>
+      <x:c r="L6" s="7" t="str"/>
+      <x:c r="M6" s="7" t="str">
+        <x:v>../datasheets/C54582078/SLESD11LE5.0C.pdf</x:v>
+      </x:c>
+      <x:c r="N6" s="7" t="str">
+        <x:v>${LCSC_LIB_ROOT}/Circuit Protection/Circuit Protection.3dshapes/DFN0603-2L-BI-1.wrl</x:v>
+      </x:c>
+      <x:c r="O6" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P6" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q6" s="7" t="str">
+        <x:v>DFN0603-2L</x:v>
+      </x:c>
+      <x:c r="R6" s="7" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C54582078.html</x:v>
+      </x:c>
+      <x:c r="S6" s="7" t="str">
+        <x:v>Package: DFN0603-2L; Reverse Stand-Off Voltage: 5.0V; Capacitance: 0.3pF; Peak Pulse Current: 5.5A; ESD: ±30kV</x:v>
+      </x:c>
+      <x:c r="T6" s="7" t="str">
+        <x:v>Requested ESD diode; replaces legacy placeholder C9900301658.</x:v>
+      </x:c>
+      <x:c r="U6" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V6" s="7" t="str">
+        <x:v>LocalParts</x:v>
+      </x:c>
+      <x:c r="W6" s="7" t="str">
+        <x:v>Circuit Protection</x:v>
+      </x:c>
+      <x:c r="X6" s="7" t="str">
+        <x:v>Circuit Protection.kicad_sym</x:v>
+      </x:c>
+      <x:c r="Y6" s="7" t="str">
+        <x:v>Circuit Protection.pretty</x:v>
+      </x:c>
+      <x:c r="Z6" s="7" t="str">
+        <x:v>CONVERTED</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="U5:U5">
+  <x:conditionalFormatting sqref="U5:U6">
     <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="CLASSIFIED_PARTIAL"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="Z5:Z5">
+  <x:conditionalFormatting sqref="Z5:Z6">
     <x:cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="PENDING_CONVERSION"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b90cace0e404bd2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50035eac798748dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10190,7 +10874,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="str">
-        <x:v>类别：Connectors；记录数：7；来源：library_index.csv</x:v>
+        <x:v>类别：Connectors；记录数：8；来源：library_index.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -10501,42 +11185,42 @@
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>C2937625</x:v>
+        <x:v>C2925430</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>PZ254V-11-03P</x:v>
+        <x:v>BM29B0.6-2DS/2-0.35V</x:v>
       </x:c>
       <x:c r="C8" s="7" t="str">
-        <x:v>XFCN</x:v>
+        <x:v>HRS(广濑)</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>Pin Header 3 Position 2.54mm Pitch Single Row Through Hole -40℃~+105℃</x:v>
+        <x:v>4-pin 0.35mm pitch board-to-board connector</x:v>
       </x:c>
       <x:c r="E8" s="7" t="str">
         <x:v>Connectors/Headers, Male Pins</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
-        <x:v>PZ254V-11-03P_C2937625</x:v>
+        <x:v>BM29B0.6-2DS_2-0.35V</x:v>
       </x:c>
       <x:c r="G8" s="7" t="str">
-        <x:v>HDR-TH_3P-P2.54-V-M_PZ254V-11-03P</x:v>
+        <x:v>BM29B0.6-2DS_2-0.35V</x:v>
       </x:c>
       <x:c r="H8" s="7" t="str">
-        <x:v>10</x:v>
+        <x:v>BM29B0.6-2DS/2-0.35V</x:v>
       </x:c>
       <x:c r="I8" s="7" t="str">
-        <x:v>Through Hole,P=2.54mm</x:v>
+        <x:v>SMD,P=0.35mm</x:v>
       </x:c>
       <x:c r="J8" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/3b85a1cdf6ed945f2e278f00c1e42442.pdf?productCode=C2937625</x:v>
+        <x:v>https://atta.szlcsc.com/upload/public/pdf/source/20211126/440829653A41B2C50D4B12C1CE909750.pdf</x:v>
       </x:c>
       <x:c r="K8" s="7" t="str"/>
       <x:c r="L8" s="7" t="str"/>
       <x:c r="M8" s="7" t="str">
-        <x:v>../datasheets/C2937625/PZ254V-11-03P.pdf</x:v>
+        <x:v>../datasheets/C2925430/BM29B0.6-2DS_2-0.35V.pdf</x:v>
       </x:c>
       <x:c r="N8" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Connectors/Connectors.3dshapes/HDR-TH_3P-P2.54-V-M_PZ254V-11-03P.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Connectors/Connectors.3dshapes/CONN-SMD_10P-P0.35_HRS_BM29B0.6-2DS-2-0.35V-51.wrl</x:v>
       </x:c>
       <x:c r="O8" s="7" t="str">
         <x:v>Active</x:v>
@@ -10545,22 +11229,22 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str">
-        <x:v>烧录口</x:v>
+        <x:v>SMD,P=0.35mm</x:v>
       </x:c>
       <x:c r="R8" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C2937625.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C2925430.html</x:v>
       </x:c>
       <x:c r="S8" s="7" t="str">
-        <x:v>Package: Through Hole,P=2.54mm; Connector Type: Through Hole; Voltage Rating (Max): 250V; Contact Material: Brass; Number of Rows: 1; Pitch: 2.54mm; Circluar Pins/Square Pins: Square pin; Current Rating: 3A; Supplementary Features: -; Insulation Height: 2.5mm; Length of Mating Pin: 6.1mm; Contact Plating: Gold; Number of PINs: 3P; Operating Temperature: -40℃~+105℃; Length of End Connection Pin: 3mm; Color: Black; Row Spacing: -; Pin Structure: 1x3P</x:v>
+        <x:v>Package: SMD; Pitch: 0.35mm; Pins: 4</x:v>
       </x:c>
       <x:c r="T8" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: J3</x:v>
+        <x:v>EBOM BOM_QS01_GD32F503_V1.10; designator J2.</x:v>
       </x:c>
       <x:c r="U8" s="7" t="str">
         <x:v>METADATA_READY</x:v>
       </x:c>
       <x:c r="V8" s="7" t="str">
-        <x:v>legacy_import</x:v>
+        <x:v>EBOM_V1.10</x:v>
       </x:c>
       <x:c r="W8" s="7" t="str">
         <x:v>Connectors</x:v>
@@ -10577,42 +11261,42 @@
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>C492420</x:v>
+        <x:v>C2937625</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>PZ254V-12-6P</x:v>
+        <x:v>PZ254V-11-03P</x:v>
       </x:c>
       <x:c r="C9" s="7" t="str">
         <x:v>XFCN</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>Pin Header 6 Position 2.54mm Pitch Dual Row Through Hole -40℃~+105℃</x:v>
+        <x:v>Pin Header 3 Position 2.54mm Pitch Single Row Through Hole -40℃~+105℃</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
         <x:v>Connectors/Headers, Male Pins</x:v>
       </x:c>
       <x:c r="F9" s="7" t="str">
-        <x:v>PZ254V-12-6P</x:v>
+        <x:v>PZ254V-11-03P_C2937625</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
-        <x:v>HDR-TH_6P-P2.54-V-M-R2-C3-S2.54</x:v>
+        <x:v>HDR-TH_3P-P2.54-V-M_PZ254V-11-03P</x:v>
       </x:c>
       <x:c r="H9" s="7" t="str">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I9" s="7" t="str">
         <x:v>Through Hole,P=2.54mm</x:v>
       </x:c>
       <x:c r="J9" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/50ec9710cee52ae98bff43fbb8887c5b.pdf?productCode=C492420</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/3b85a1cdf6ed945f2e278f00c1e42442.pdf?productCode=C2937625</x:v>
       </x:c>
       <x:c r="K9" s="7" t="str"/>
       <x:c r="L9" s="7" t="str"/>
       <x:c r="M9" s="7" t="str">
-        <x:v>../datasheets/C492420/PZ254V-12-6P.pdf</x:v>
+        <x:v>../datasheets/C2937625/PZ254V-11-03P.pdf</x:v>
       </x:c>
       <x:c r="N9" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Connectors/Connectors.3dshapes/HDR-TH_6P-P2.54-V-M-R2-C3-S2.54.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Connectors/Connectors.3dshapes/HDR-TH_3P-P2.54-V-M_PZ254V-11-03P.wrl</x:v>
       </x:c>
       <x:c r="O9" s="7" t="str">
         <x:v>Active</x:v>
@@ -10621,16 +11305,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q9" s="7" t="str">
-        <x:v>6PIN烧录孔</x:v>
+        <x:v>烧录口</x:v>
       </x:c>
       <x:c r="R9" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C492420.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C2937625.html</x:v>
       </x:c>
       <x:c r="S9" s="7" t="str">
-        <x:v>Package: Through Hole,P=2.54mm; Connector Type: Through Hole; Voltage Rating (Max): -; Contact Material: Brass; Number of Rows: 2; Pitch: 2.54mm; Circluar Pins/Square Pins: Square pin; Current Rating: 3A; Insulation Height: 2.5mm; Length of Mating Pin: 6mm; Number of PINs: 6P; Operating Temperature: -40℃~+105℃; Length of End Connection Pin: 3mm; Contact Plating: Gold; Color: Black; Pin Structure: 2x3P; Row Spacing: 2.54mm</x:v>
+        <x:v>Package: Through Hole,P=2.54mm; Connector Type: Through Hole; Voltage Rating (Max): 250V; Contact Material: Brass; Number of Rows: 1; Pitch: 2.54mm; Circluar Pins/Square Pins: Square pin; Current Rating: 3A; Supplementary Features: -; Insulation Height: 2.5mm; Length of Mating Pin: 6.1mm; Contact Plating: Gold; Number of PINs: 3P; Operating Temperature: -40℃~+105℃; Length of End Connection Pin: 3mm; Color: Black; Row Spacing: -; Pin Structure: 1x3P</x:v>
       </x:c>
       <x:c r="T9" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: J8</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: J3</x:v>
       </x:c>
       <x:c r="U9" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -10653,42 +11337,42 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>C5138889</x:v>
+        <x:v>C492420</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>GPCA101-0502A001C1AA</x:v>
+        <x:v>PZ254V-12-6P</x:v>
       </x:c>
       <x:c r="C10" s="7" t="str">
-        <x:v>GREENCONN</x:v>
+        <x:v>XFCN</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>Pin Header 5 Position 1mm Pitch Single Row Through Hole -40℃~+105℃</x:v>
+        <x:v>Pin Header 6 Position 2.54mm Pitch Dual Row Through Hole -40℃~+105℃</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
         <x:v>Connectors/Headers, Male Pins</x:v>
       </x:c>
       <x:c r="F10" s="7" t="str">
-        <x:v>GPCA101-0502A001C1AA</x:v>
+        <x:v>PZ254V-12-6P</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
-        <x:v>CONN-TH_GREENCONN_GPCA101-0502A001C1AA</x:v>
+        <x:v>HDR-TH_6P-P2.54-V-M-R2-C3-S2.54</x:v>
       </x:c>
       <x:c r="H10" s="7" t="str">
-        <x:v>GPCA101-0502A</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="I10" s="7" t="str">
-        <x:v>Through Hole,P=1mm</x:v>
+        <x:v>Through Hole,P=2.54mm</x:v>
       </x:c>
       <x:c r="J10" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/9791ba8c859df0647813150b8f9162a2.pdf?productCode=C5138889</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/50ec9710cee52ae98bff43fbb8887c5b.pdf?productCode=C492420</x:v>
       </x:c>
       <x:c r="K10" s="7" t="str"/>
       <x:c r="L10" s="7" t="str"/>
       <x:c r="M10" s="7" t="str">
-        <x:v>../datasheets/C5138889/GPCA101-0502A001C1AA.pdf</x:v>
+        <x:v>../datasheets/C492420/PZ254V-12-6P.pdf</x:v>
       </x:c>
       <x:c r="N10" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Connectors/Connectors.3dshapes/CONN-TH_GREENCONN_GPCA101-0502A001C1AA.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Connectors/Connectors.3dshapes/HDR-TH_6P-P2.54-V-M-R2-C3-S2.54.wrl</x:v>
       </x:c>
       <x:c r="O10" s="7" t="str">
         <x:v>Active</x:v>
@@ -10697,16 +11381,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str">
-        <x:v>插件</x:v>
+        <x:v>6PIN烧录孔</x:v>
       </x:c>
       <x:c r="R10" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C5138889.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C492420.html</x:v>
       </x:c>
       <x:c r="S10" s="7" t="str">
-        <x:v>Package: Through Hole,P=1mm; Connector Type: Through Hole; Pitch: 1mm; Circluar Pins/Square Pins: Square pin; Current Rating: 1A; Insulation Height: 1mm; Length of Mating Pin: 3.55mm; Contact Plating: Gold; Length of End Connection Pin: 1.8mm; Contact Material: Phosphor bronze; Number of PINs: 5P; Operating Temperature: -40℃~+105℃; Pin Structure: 1x5P; Number of Rows: 1</x:v>
+        <x:v>Package: Through Hole,P=2.54mm; Connector Type: Through Hole; Voltage Rating (Max): -; Contact Material: Brass; Number of Rows: 2; Pitch: 2.54mm; Circluar Pins/Square Pins: Square pin; Current Rating: 3A; Insulation Height: 2.5mm; Length of Mating Pin: 6mm; Number of PINs: 6P; Operating Temperature: -40℃~+105℃; Length of End Connection Pin: 3mm; Contact Plating: Gold; Color: Black; Pin Structure: 2x3P; Row Spacing: 2.54mm</x:v>
       </x:c>
       <x:c r="T10" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: J11</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: J8</x:v>
       </x:c>
       <x:c r="U10" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -10729,42 +11413,42 @@
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>C54334395</x:v>
+        <x:v>C5138889</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>GT-A0801WRS-108BBT01</x:v>
+        <x:v>GPCA101-0502A001C1AA</x:v>
       </x:c>
       <x:c r="C11" s="7" t="str">
-        <x:v>G-Switch</x:v>
+        <x:v>GREENCONN</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str">
-        <x:v>Surface Mount, Right Angle 100V 8 1 0.8mm 800mA 8P -40℃~+85℃ Tin Black 1x8P SMD,P=0.8mm,Surface Mount,Right Angle Headers, Male Pins</x:v>
+        <x:v>Pin Header 5 Position 1mm Pitch Single Row Through Hole -40℃~+105℃</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
         <x:v>Connectors/Headers, Male Pins</x:v>
       </x:c>
       <x:c r="F11" s="7" t="str">
-        <x:v>GT-A0801WRS-108BBT01</x:v>
+        <x:v>GPCA101-0502A001C1AA</x:v>
       </x:c>
       <x:c r="G11" s="7" t="str">
-        <x:v>CONN-SMD_GT-A0801WRS-108BBT01</x:v>
+        <x:v>CONN-TH_GREENCONN_GPCA101-0502A001C1AA</x:v>
       </x:c>
       <x:c r="H11" s="7" t="str">
-        <x:v>9990000051497</x:v>
+        <x:v>GPCA101-0502A</x:v>
       </x:c>
       <x:c r="I11" s="7" t="str">
-        <x:v>SMD,P=0.8mm,Surface Mount,Right Angle</x:v>
+        <x:v>Through Hole,P=1mm</x:v>
       </x:c>
       <x:c r="J11" s="7" t="str">
-        <x:v>https://datasheet.lcsc.com/datasheet/pdf/280a0ac82606d05a19e9b62f8ac57389.pdf?productCode=C54334395</x:v>
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/9791ba8c859df0647813150b8f9162a2.pdf?productCode=C5138889</x:v>
       </x:c>
       <x:c r="K11" s="7" t="str"/>
       <x:c r="L11" s="7" t="str"/>
       <x:c r="M11" s="7" t="str">
-        <x:v>../datasheets/C54334395/GT-A0801WRS-108BBT01.pdf</x:v>
+        <x:v>../datasheets/C5138889/GPCA101-0502A001C1AA.pdf</x:v>
       </x:c>
       <x:c r="N11" s="7" t="str">
-        <x:v>${LCSC_LIB_ROOT}/Connectors/Connectors.3dshapes/CONN-SMD_GT-A0801WRS-108BBT01.wrl</x:v>
+        <x:v>${LCSC_LIB_ROOT}/Connectors/Connectors.3dshapes/CONN-TH_GREENCONN_GPCA101-0502A001C1AA.wrl</x:v>
       </x:c>
       <x:c r="O11" s="7" t="str">
         <x:v>Active</x:v>
@@ -10773,16 +11457,16 @@
         <x:v>LCSC</x:v>
       </x:c>
       <x:c r="Q11" s="7" t="str">
-        <x:v>接插件</x:v>
+        <x:v>插件</x:v>
       </x:c>
       <x:c r="R11" s="7" t="str">
-        <x:v>https://www.lcsc.com/product-detail/C54334395.html</x:v>
+        <x:v>https://www.lcsc.com/product-detail/C5138889.html</x:v>
       </x:c>
       <x:c r="S11" s="7" t="str">
-        <x:v>Package: SMD,P=0.8mm,Surface Mount,Right Angle; Connector Type: Surface Mount, Right Angle; Voltage Rating (Max): 100V; Contact Material: Brass; Number of PINs Per Row: 8; Number of Rows: 1; Pitch: 0.8mm; Current Rating: 800mA; Flame Retardant Rating: UL94V-0; Number of PINs: 8P; Operating Temperature: -40℃~+85℃; Contact Plating: Tin; Plastic Material: LCP; Color: Black; Pin Structure: 1x8P</x:v>
+        <x:v>Package: Through Hole,P=1mm; Connector Type: Through Hole; Pitch: 1mm; Circluar Pins/Square Pins: Square pin; Current Rating: 1A; Insulation Height: 1mm; Length of Mating Pin: 3.55mm; Contact Plating: Gold; Length of End Connection Pin: 1.8mm; Contact Material: Phosphor bronze; Number of PINs: 5P; Operating Temperature: -40℃~+105℃; Pin Structure: 1x5P; Number of Rows: 1</x:v>
       </x:c>
       <x:c r="T11" s="7" t="str">
-        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: J9</x:v>
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: J11</x:v>
       </x:c>
       <x:c r="U11" s="7" t="str">
         <x:v>METADATA_READY</x:v>
@@ -10803,16 +11487,92 @@
         <x:v>CONVERTED</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="7" t="str">
+        <x:v>C54334395</x:v>
+      </x:c>
+      <x:c r="B12" s="7" t="str">
+        <x:v>GT-A0801WRS-108BBT01</x:v>
+      </x:c>
+      <x:c r="C12" s="7" t="str">
+        <x:v>G-Switch</x:v>
+      </x:c>
+      <x:c r="D12" s="7" t="str">
+        <x:v>Surface Mount, Right Angle 100V 8 1 0.8mm 800mA 8P -40℃~+85℃ Tin Black 1x8P SMD,P=0.8mm,Surface Mount,Right Angle Headers, Male Pins</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="str">
+        <x:v>Connectors/Headers, Male Pins</x:v>
+      </x:c>
+      <x:c r="F12" s="7" t="str">
+        <x:v>GT-A0801WRS-108BBT01</x:v>
+      </x:c>
+      <x:c r="G12" s="7" t="str">
+        <x:v>CONN-SMD_GT-A0801WRS-108BBT01</x:v>
+      </x:c>
+      <x:c r="H12" s="7" t="str">
+        <x:v>9990000051497</x:v>
+      </x:c>
+      <x:c r="I12" s="7" t="str">
+        <x:v>SMD,P=0.8mm,Surface Mount,Right Angle</x:v>
+      </x:c>
+      <x:c r="J12" s="7" t="str">
+        <x:v>https://datasheet.lcsc.com/datasheet/pdf/280a0ac82606d05a19e9b62f8ac57389.pdf?productCode=C54334395</x:v>
+      </x:c>
+      <x:c r="K12" s="7" t="str"/>
+      <x:c r="L12" s="7" t="str"/>
+      <x:c r="M12" s="7" t="str">
+        <x:v>../datasheets/C54334395/GT-A0801WRS-108BBT01.pdf</x:v>
+      </x:c>
+      <x:c r="N12" s="7" t="str">
+        <x:v>${LCSC_LIB_ROOT}/Connectors/Connectors.3dshapes/CONN-SMD_GT-A0801WRS-108BBT01.wrl</x:v>
+      </x:c>
+      <x:c r="O12" s="7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="P12" s="7" t="str">
+        <x:v>LCSC</x:v>
+      </x:c>
+      <x:c r="Q12" s="7" t="str">
+        <x:v>接插件</x:v>
+      </x:c>
+      <x:c r="R12" s="7" t="str">
+        <x:v>https://www.lcsc.com/product-detail/C54334395.html</x:v>
+      </x:c>
+      <x:c r="S12" s="7" t="str">
+        <x:v>Package: SMD,P=0.8mm,Surface Mount,Right Angle; Connector Type: Surface Mount, Right Angle; Voltage Rating (Max): 100V; Contact Material: Brass; Number of PINs Per Row: 8; Number of Rows: 1; Pitch: 0.8mm; Current Rating: 800mA; Flame Retardant Rating: UL94V-0; Number of PINs: 8P; Operating Temperature: -40℃~+85℃; Contact Plating: Tin; Plastic Material: LCP; Color: Black; Pin Structure: 1x8P</x:v>
+      </x:c>
+      <x:c r="T12" s="7" t="str">
+        <x:v>Sources: BOM_PASTER_8984112A_Y182.xls; Designators: BOM_PASTER_8984112A_Y182.xls: J9</x:v>
+      </x:c>
+      <x:c r="U12" s="7" t="str">
+        <x:v>METADATA_READY</x:v>
+      </x:c>
+      <x:c r="V12" s="7" t="str">
+        <x:v>legacy_import</x:v>
+      </x:c>
+      <x:c r="W12" s="7" t="str">
+        <x:v>Connectors</x:v>
+      </x:c>
+      <x:c r="X12" s="7" t="str">
+        <x:v>Connectors.kicad_sym</x:v>
+      </x:c>
+      <x:c r="Y12" s="7" t="str">
+        <x:v>Connectors.pretty</x:v>
+      </x:c>
+      <x:c r="Z12" s="7" t="str">
+        <x:v>CONVERTED</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="U5:U11">
+  <x:conditionalFormatting sqref="U5:U12">
     <x:cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="CLASSIFIED_PARTIAL"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="Z5:Z11">
+  <x:conditionalFormatting sqref="Z5:Z12">
     <x:cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="PENDING_CONVERSION"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf425cb23fd1c4374"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6df48f4d58e4539"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11024,7 +11784,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1229f437eb84356"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd55ed4a1597f4ed6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11312,7 +12072,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0109a59265664d1b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc190a583d66e41e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11596,7 +12356,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06c80c9fab90453c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33ebef9a51e94885"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11884,7 +12644,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ed19bbb9e344402"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1c6251eb3cb4d7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12172,7 +12932,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11b1f23469384f9d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97b0b93522e345d4"/>
   </x:tableParts>
 </x:worksheet>
 </file>